--- a/data/uploads/tongshi_demo.xlsx
+++ b/data/uploads/tongshi_demo.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11740"/>
+    <workbookView windowWidth="28000" windowHeight="11740"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$Z$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$Z$352</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="2596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4412" uniqueCount="2796">
   <si>
     <t>日期</t>
   </si>
@@ -7818,6 +7818,606 @@
   </si>
   <si>
     <t>11343</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>1130</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>0.00166863</t>
+  </si>
+  <si>
+    <t>46737</t>
+  </si>
+  <si>
+    <t>10188</t>
+  </si>
+  <si>
+    <t>754</t>
+  </si>
+  <si>
+    <t>643</t>
+  </si>
+  <si>
+    <t>212341</t>
+  </si>
+  <si>
+    <t>47167</t>
+  </si>
+  <si>
+    <t>11030</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.00455927</t>
+  </si>
+  <si>
+    <t>94074</t>
+  </si>
+  <si>
+    <t>27636</t>
+  </si>
+  <si>
+    <t>8224</t>
+  </si>
+  <si>
+    <t>4888</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>552763</t>
+  </si>
+  <si>
+    <t>239202</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>30456</t>
+  </si>
+  <si>
+    <t>0.00086640</t>
+  </si>
+  <si>
+    <t>361491</t>
+  </si>
+  <si>
+    <t>85411</t>
+  </si>
+  <si>
+    <t>8061</t>
+  </si>
+  <si>
+    <t>6529</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>1765600</t>
+  </si>
+  <si>
+    <t>478946</t>
+  </si>
+  <si>
+    <t>93060</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>0.00178137</t>
+  </si>
+  <si>
+    <t>214156</t>
+  </si>
+  <si>
+    <t>46032</t>
+  </si>
+  <si>
+    <t>4935</t>
+  </si>
+  <si>
+    <t>3988</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>1081194</t>
+  </si>
+  <si>
+    <t>382224</t>
+  </si>
+  <si>
+    <t>1.29</t>
+  </si>
+  <si>
+    <t>52184</t>
+  </si>
+  <si>
+    <t>0.01726593</t>
+  </si>
+  <si>
+    <t>18685</t>
+  </si>
+  <si>
+    <t>5618</t>
+  </si>
+  <si>
+    <t>2223</t>
+  </si>
+  <si>
+    <t>1363</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>162449</t>
+  </si>
+  <si>
+    <t>98896</t>
+  </si>
+  <si>
+    <t>6917</t>
+  </si>
+  <si>
+    <t>0.00177368</t>
+  </si>
+  <si>
+    <t>68079</t>
+  </si>
+  <si>
+    <t>16914</t>
+  </si>
+  <si>
+    <t>710</t>
+  </si>
+  <si>
+    <t>313298</t>
+  </si>
+  <si>
+    <t>55859</t>
+  </si>
+  <si>
+    <t>18025</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>0.00230428</t>
+  </si>
+  <si>
+    <t>469489</t>
+  </si>
+  <si>
+    <t>121079</t>
+  </si>
+  <si>
+    <t>25118</t>
+  </si>
+  <si>
+    <t>17983</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>2913673</t>
+  </si>
+  <si>
+    <t>1223437</t>
+  </si>
+  <si>
+    <t>138097</t>
+  </si>
+  <si>
+    <t>0.00074264</t>
+  </si>
+  <si>
+    <t>743312</t>
+  </si>
+  <si>
+    <t>195249</t>
+  </si>
+  <si>
+    <t>19908</t>
+  </si>
+  <si>
+    <t>16480</t>
+  </si>
+  <si>
+    <t>4240465</t>
+  </si>
+  <si>
+    <t>1163770</t>
+  </si>
+  <si>
+    <t>214580</t>
+  </si>
+  <si>
+    <t>0.00472740</t>
+  </si>
+  <si>
+    <t>205145</t>
+  </si>
+  <si>
+    <t>57960</t>
+  </si>
+  <si>
+    <t>13626</t>
+  </si>
+  <si>
+    <t>9334</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>1254303</t>
+  </si>
+  <si>
+    <t>503013</t>
+  </si>
+  <si>
+    <t>64439</t>
+  </si>
+  <si>
+    <t>0.00085397</t>
+  </si>
+  <si>
+    <t>154217</t>
+  </si>
+  <si>
+    <t>51524</t>
+  </si>
+  <si>
+    <t>3307</t>
+  </si>
+  <si>
+    <t>2801</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>1024172</t>
+  </si>
+  <si>
+    <t>159160</t>
+  </si>
+  <si>
+    <t>54967</t>
+  </si>
+  <si>
+    <t>0.00551861</t>
+  </si>
+  <si>
+    <t>175894</t>
+  </si>
+  <si>
+    <t>35335</t>
+  </si>
+  <si>
+    <t>10831</t>
+  </si>
+  <si>
+    <t>7383</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>1039132</t>
+  </si>
+  <si>
+    <t>604271</t>
+  </si>
+  <si>
+    <t>43659</t>
+  </si>
+  <si>
+    <t>0.01804024</t>
+  </si>
+  <si>
+    <t>64457</t>
+  </si>
+  <si>
+    <t>20676</t>
+  </si>
+  <si>
+    <t>8093</t>
+  </si>
+  <si>
+    <t>5429</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>633974</t>
+  </si>
+  <si>
+    <t>395182</t>
+  </si>
+  <si>
+    <t>25866</t>
+  </si>
+  <si>
+    <t>0.00190375</t>
+  </si>
+  <si>
+    <t>192864</t>
+  </si>
+  <si>
+    <t>56205</t>
+  </si>
+  <si>
+    <t>2969</t>
+  </si>
+  <si>
+    <t>2582</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>1092150</t>
+  </si>
+  <si>
+    <t>183219</t>
+  </si>
+  <si>
+    <t>59921</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>0.00304233</t>
+  </si>
+  <si>
+    <t>432304</t>
+  </si>
+  <si>
+    <t>105840</t>
+  </si>
+  <si>
+    <t>26735</t>
+  </si>
+  <si>
+    <t>18736</t>
+  </si>
+  <si>
+    <t>2666715</t>
+  </si>
+  <si>
+    <t>1265835</t>
+  </si>
+  <si>
+    <t>122904</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>0.00100737</t>
+  </si>
+  <si>
+    <t>566542</t>
+  </si>
+  <si>
+    <t>139968</t>
+  </si>
+  <si>
+    <t>12312</t>
+  </si>
+  <si>
+    <t>10120</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>2981253</t>
+  </si>
+  <si>
+    <t>806093</t>
+  </si>
+  <si>
+    <t>153821</t>
+  </si>
+  <si>
+    <t>0.00813421</t>
+  </si>
+  <si>
+    <t>3714</t>
+  </si>
+  <si>
+    <t>1967</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>846</t>
+  </si>
+  <si>
+    <t>55014</t>
+  </si>
+  <si>
+    <t>34469</t>
+  </si>
+  <si>
+    <t>2320</t>
+  </si>
+  <si>
+    <t>0.00088210</t>
+  </si>
+  <si>
+    <t>108689</t>
+  </si>
+  <si>
+    <t>26074</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>1380</t>
+  </si>
+  <si>
+    <t>496055</t>
+  </si>
+  <si>
+    <t>87536</t>
+  </si>
+  <si>
+    <t>27761</t>
+  </si>
+  <si>
+    <t>0.00672665</t>
+  </si>
+  <si>
+    <t>133257</t>
+  </si>
+  <si>
+    <t>23786</t>
+  </si>
+  <si>
+    <t>8287</t>
+  </si>
+  <si>
+    <t>5686</t>
+  </si>
+  <si>
+    <t>786677</t>
+  </si>
+  <si>
+    <t>507587</t>
+  </si>
+  <si>
+    <t>30838</t>
+  </si>
+  <si>
+    <t>0.00459141</t>
+  </si>
+  <si>
+    <t>293769</t>
+  </si>
+  <si>
+    <t>88426</t>
+  </si>
+  <si>
+    <t>18581</t>
+  </si>
+  <si>
+    <t>12423</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>1850595</t>
+  </si>
+  <si>
+    <t>726084</t>
+  </si>
+  <si>
+    <t>98052</t>
+  </si>
+  <si>
+    <t>0.02077890</t>
+  </si>
+  <si>
+    <t>108174</t>
+  </si>
+  <si>
+    <t>32533</t>
+  </si>
+  <si>
+    <t>10981</t>
+  </si>
+  <si>
+    <t>7583</t>
+  </si>
+  <si>
+    <t>676</t>
+  </si>
+  <si>
+    <t>1079653</t>
+  </si>
+  <si>
+    <t>675233</t>
+  </si>
+  <si>
+    <t>42056</t>
+  </si>
+  <si>
+    <t>0.04736842</t>
+  </si>
+  <si>
+    <t>1272</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>29181</t>
+  </si>
+  <si>
+    <t>22551</t>
+  </si>
+  <si>
+    <t>880</t>
+  </si>
+  <si>
+    <t>0.00123097</t>
+  </si>
+  <si>
+    <t>214475</t>
+  </si>
+  <si>
+    <t>57678</t>
+  </si>
+  <si>
+    <t>3125</t>
+  </si>
+  <si>
+    <t>2734</t>
+  </si>
+  <si>
+    <t>1070946</t>
+  </si>
+  <si>
+    <t>177236</t>
+  </si>
+  <si>
+    <t>61251</t>
   </si>
 </sst>
 </file>
@@ -7839,15 +8439,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -8445,11 +9045,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8833,7 +9435,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:Z352"/>
+  <dimension ref="A1:Z387"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.0192307692308" style="1" customWidth="1"/>
@@ -10619,7 +11221,6 @@
       <c r="C44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
         <v>25</v>
       </c>
@@ -10641,7 +11242,6 @@
       <c r="K44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>26</v>
       </c>
@@ -12935,7 +13535,6 @@
       <c r="K100" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L100" s="1"/>
       <c r="M100" s="1" t="s">
         <v>157</v>
       </c>
@@ -13876,7 +14475,6 @@
       <c r="K123" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L123" s="1"/>
       <c r="M123" s="1" t="s">
         <v>149</v>
       </c>
@@ -14366,7 +14964,6 @@
       <c r="K135" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L135" s="1"/>
       <c r="M135" s="1" t="s">
         <v>364</v>
       </c>
@@ -14668,7 +15265,6 @@
       <c r="C143" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D143" s="1"/>
       <c r="E143" s="1" t="s">
         <v>262</v>
       </c>
@@ -14690,7 +15286,6 @@
       <c r="K143" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L143" s="1"/>
       <c r="M143" s="1" t="s">
         <v>26</v>
       </c>
@@ -16167,7 +16762,6 @@
       <c r="K179" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L179" s="1"/>
       <c r="M179" s="1" t="s">
         <v>1219</v>
       </c>
@@ -20962,7 +21556,6 @@
       <c r="K296" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L296" s="1"/>
       <c r="M296" s="1" t="s">
         <v>1219</v>
       </c>
@@ -23261,20 +23854,1455 @@
         <v>2595</v>
       </c>
     </row>
+    <row r="353" spans="1:13">
+      <c r="A353" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>2190</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G353" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J353" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="K353" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="L353" s="4" t="s">
+        <v>2598</v>
+      </c>
+      <c r="M353" s="4" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13">
+      <c r="A354" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>2602</v>
+      </c>
+      <c r="G354" s="4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="H354" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="I354" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J354" s="4" t="s">
+        <v>2605</v>
+      </c>
+      <c r="K354" s="4" t="s">
+        <v>2606</v>
+      </c>
+      <c r="L354" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="M354" s="4" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13">
+      <c r="A355" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B355" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C355" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E355" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="F355" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G355" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H355" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="I355" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J355" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="K355" s="4" t="s">
+        <v>2608</v>
+      </c>
+      <c r="L355" s="4" t="s">
+        <v>2609</v>
+      </c>
+      <c r="M355" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13">
+      <c r="A356" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B356" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E356" s="4" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F356" s="4" t="s">
+        <v>2612</v>
+      </c>
+      <c r="G356" s="4" t="s">
+        <v>2613</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>2614</v>
+      </c>
+      <c r="I356" s="4" t="s">
+        <v>2615</v>
+      </c>
+      <c r="J356" s="4" t="s">
+        <v>2616</v>
+      </c>
+      <c r="K356" s="4" t="s">
+        <v>2617</v>
+      </c>
+      <c r="L356" s="4" t="s">
+        <v>2618</v>
+      </c>
+      <c r="M356" s="4" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13">
+      <c r="A357" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B357" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="E357" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="F357" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="G357" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="H357" s="4" t="s">
+        <v>2624</v>
+      </c>
+      <c r="I357" s="4" t="s">
+        <v>2625</v>
+      </c>
+      <c r="J357" s="4" t="s">
+        <v>2626</v>
+      </c>
+      <c r="K357" s="4" t="s">
+        <v>2627</v>
+      </c>
+      <c r="L357" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M357" s="4" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="358" spans="1:13">
+      <c r="A358" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E358" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="F358" s="4" t="s">
+        <v>2608</v>
+      </c>
+      <c r="G358" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="H358" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="I358" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J358" s="4" t="s">
+        <v>2629</v>
+      </c>
+      <c r="K358" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="L358" s="4" t="s">
+        <v>2630</v>
+      </c>
+      <c r="M358" s="4" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13">
+      <c r="A359" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B359" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C359" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>2631</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>2632</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>2633</v>
+      </c>
+      <c r="G359" s="4" t="s">
+        <v>2634</v>
+      </c>
+      <c r="H359" s="4" t="s">
+        <v>2635</v>
+      </c>
+      <c r="I359" s="4" t="s">
+        <v>2636</v>
+      </c>
+      <c r="J359" s="4" t="s">
+        <v>2637</v>
+      </c>
+      <c r="K359" s="4" t="s">
+        <v>2638</v>
+      </c>
+      <c r="L359" s="4" t="s">
+        <v>2639</v>
+      </c>
+      <c r="M359" s="4" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13">
+      <c r="A360" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>2641</v>
+      </c>
+      <c r="E360" s="4" t="s">
+        <v>2642</v>
+      </c>
+      <c r="F360" s="4" t="s">
+        <v>2643</v>
+      </c>
+      <c r="G360" s="4" t="s">
+        <v>2644</v>
+      </c>
+      <c r="H360" s="4" t="s">
+        <v>2645</v>
+      </c>
+      <c r="I360" s="4" t="s">
+        <v>2646</v>
+      </c>
+      <c r="J360" s="4" t="s">
+        <v>2647</v>
+      </c>
+      <c r="K360" s="4" t="s">
+        <v>2648</v>
+      </c>
+      <c r="L360" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="M360" s="4" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13">
+      <c r="A361" s="4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B361" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E361" s="4" t="s">
+        <v>2651</v>
+      </c>
+      <c r="F361" s="4" t="s">
+        <v>2652</v>
+      </c>
+      <c r="G361" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>2653</v>
+      </c>
+      <c r="I361" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="J361" s="4" t="s">
+        <v>2654</v>
+      </c>
+      <c r="K361" s="4" t="s">
+        <v>2655</v>
+      </c>
+      <c r="L361" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M361" s="4" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13">
+      <c r="A362" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D362" s="1">
+        <v>0.00334165</v>
+      </c>
+      <c r="E362" s="1">
+        <v>302768</v>
+      </c>
+      <c r="F362" s="1">
+        <v>72120</v>
+      </c>
+      <c r="G362" s="1">
+        <v>20279</v>
+      </c>
+      <c r="H362" s="1">
+        <v>14107</v>
+      </c>
+      <c r="I362" s="1">
+        <v>241</v>
+      </c>
+      <c r="J362" s="1">
+        <v>1879967</v>
+      </c>
+      <c r="K362" s="1">
+        <v>940101</v>
+      </c>
+      <c r="L362" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="M362" s="1">
+        <v>84502</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13">
+      <c r="A363" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D363" s="1">
+        <v>0.00122588</v>
+      </c>
+      <c r="E363" s="1">
+        <v>127821</v>
+      </c>
+      <c r="F363" s="1">
+        <v>34261</v>
+      </c>
+      <c r="G363" s="1">
+        <v>2523</v>
+      </c>
+      <c r="H363" s="1">
+        <v>2112</v>
+      </c>
+      <c r="I363" s="1">
+        <v>42</v>
+      </c>
+      <c r="J363" s="1">
+        <v>706552</v>
+      </c>
+      <c r="K363" s="1">
+        <v>125712</v>
+      </c>
+      <c r="L363" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="M363" s="1">
+        <v>36748</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13">
+      <c r="A364" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D364" s="1">
+        <v>0.00068393</v>
+      </c>
+      <c r="E364" s="1">
+        <v>827314</v>
+      </c>
+      <c r="F364" s="1">
+        <v>214934</v>
+      </c>
+      <c r="G364" s="1">
+        <v>18087</v>
+      </c>
+      <c r="H364" s="1">
+        <v>15040</v>
+      </c>
+      <c r="I364" s="1">
+        <v>147</v>
+      </c>
+      <c r="J364" s="1">
+        <v>4533896</v>
+      </c>
+      <c r="K364" s="1">
+        <v>1061952</v>
+      </c>
+      <c r="L364" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="M364" s="1">
+        <v>233544</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13">
+      <c r="A365" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D365" s="1">
+        <v>0.00623557</v>
+      </c>
+      <c r="E365" s="1">
+        <v>142231</v>
+      </c>
+      <c r="F365" s="1">
+        <v>25980</v>
+      </c>
+      <c r="G365" s="1">
+        <v>10201</v>
+      </c>
+      <c r="H365" s="1">
+        <v>6689</v>
+      </c>
+      <c r="I365" s="1">
+        <v>162</v>
+      </c>
+      <c r="J365" s="1">
+        <v>840225</v>
+      </c>
+      <c r="K365" s="1">
+        <v>546831</v>
+      </c>
+      <c r="L365" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="M365" s="1">
+        <v>33338</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13">
+      <c r="A366" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D366" s="1">
+        <v>0.00546271</v>
+      </c>
+      <c r="E366" s="1">
+        <v>84915</v>
+      </c>
+      <c r="F366" s="1">
+        <v>21601</v>
+      </c>
+      <c r="G366" s="1">
+        <v>6788</v>
+      </c>
+      <c r="H366" s="1">
+        <v>4271</v>
+      </c>
+      <c r="I366" s="1">
+        <v>118</v>
+      </c>
+      <c r="J366" s="1">
+        <v>481789</v>
+      </c>
+      <c r="K366" s="1">
+        <v>228486</v>
+      </c>
+      <c r="L366" s="1">
+        <v>0.56</v>
+      </c>
+      <c r="M366" s="1">
+        <v>24434</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13">
+      <c r="A367" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D367" s="1">
+        <v>0.00101696</v>
+      </c>
+      <c r="E367" s="1">
+        <v>112031</v>
+      </c>
+      <c r="F367" s="1">
+        <v>24583</v>
+      </c>
+      <c r="G367" s="1">
+        <v>2464</v>
+      </c>
+      <c r="H367" s="1">
+        <v>1995</v>
+      </c>
+      <c r="I367" s="1">
+        <v>25</v>
+      </c>
+      <c r="J367" s="1">
+        <v>547891</v>
+      </c>
+      <c r="K367" s="1">
+        <v>159631</v>
+      </c>
+      <c r="L367" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="M367" s="1">
+        <v>27253</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13">
+      <c r="A368" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D368" s="1">
+        <v>0.00994654</v>
+      </c>
+      <c r="E368" s="1">
+        <v>50139</v>
+      </c>
+      <c r="F368" s="1">
+        <v>8043</v>
+      </c>
+      <c r="G368" s="1">
+        <v>2608</v>
+      </c>
+      <c r="H368" s="1">
+        <v>1900</v>
+      </c>
+      <c r="I368" s="1">
+        <v>80</v>
+      </c>
+      <c r="J368" s="1">
+        <v>333355</v>
+      </c>
+      <c r="K368" s="1">
+        <v>229435</v>
+      </c>
+      <c r="L368" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="M368" s="1">
+        <v>11433</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13">
+      <c r="A369" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D369" s="1">
+        <v>0.00183917</v>
+      </c>
+      <c r="E369" s="1">
+        <v>197667</v>
+      </c>
+      <c r="F369" s="1">
+        <v>58722</v>
+      </c>
+      <c r="G369" s="1">
+        <v>3329</v>
+      </c>
+      <c r="H369" s="1">
+        <v>2876</v>
+      </c>
+      <c r="I369" s="1">
+        <v>108</v>
+      </c>
+      <c r="J369" s="1">
+        <v>1137826</v>
+      </c>
+      <c r="K369" s="1">
+        <v>209398</v>
+      </c>
+      <c r="L369" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="M369" s="1">
+        <v>62864</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13">
+      <c r="A370" s="5">
+        <v>46245</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D370" s="1">
+        <v>0.01946654</v>
+      </c>
+      <c r="E370" s="1">
+        <v>92913</v>
+      </c>
+      <c r="F370" s="1">
+        <v>34829</v>
+      </c>
+      <c r="G370" s="1">
+        <v>14822</v>
+      </c>
+      <c r="H370" s="1">
+        <v>9475</v>
+      </c>
+      <c r="I370" s="1">
+        <v>678</v>
+      </c>
+      <c r="J370" s="1">
+        <v>1083922</v>
+      </c>
+      <c r="K370" s="1">
+        <v>692548</v>
+      </c>
+      <c r="L370" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="M370" s="1">
+        <v>43938</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13">
+      <c r="A371" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>2658</v>
+      </c>
+      <c r="E371" s="4" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G371" s="4" t="s">
+        <v>2661</v>
+      </c>
+      <c r="H371" s="4" t="s">
+        <v>2662</v>
+      </c>
+      <c r="I371" s="4" t="s">
+        <v>2663</v>
+      </c>
+      <c r="J371" s="4" t="s">
+        <v>2664</v>
+      </c>
+      <c r="K371" s="4" t="s">
+        <v>2665</v>
+      </c>
+      <c r="L371" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M371" s="4" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13">
+      <c r="A372" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E372" s="4" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>2669</v>
+      </c>
+      <c r="G372" s="4" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H372" s="4" t="s">
+        <v>2671</v>
+      </c>
+      <c r="I372" s="4" t="s">
+        <v>2455</v>
+      </c>
+      <c r="J372" s="4" t="s">
+        <v>2672</v>
+      </c>
+      <c r="K372" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="L372" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="M372" s="4" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13">
+      <c r="A373" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B373" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C373" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>2675</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>2676</v>
+      </c>
+      <c r="F373" s="4" t="s">
+        <v>2677</v>
+      </c>
+      <c r="G373" s="4" t="s">
+        <v>2678</v>
+      </c>
+      <c r="H373" s="4" t="s">
+        <v>2679</v>
+      </c>
+      <c r="I373" s="4" t="s">
+        <v>2680</v>
+      </c>
+      <c r="J373" s="4" t="s">
+        <v>2681</v>
+      </c>
+      <c r="K373" s="4" t="s">
+        <v>2682</v>
+      </c>
+      <c r="L373" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="M373" s="4" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13">
+      <c r="A374" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B374" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C374" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>2684</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>2685</v>
+      </c>
+      <c r="F374" s="4" t="s">
+        <v>2686</v>
+      </c>
+      <c r="G374" s="4" t="s">
+        <v>2687</v>
+      </c>
+      <c r="H374" s="4" t="s">
+        <v>2688</v>
+      </c>
+      <c r="I374" s="4" t="s">
+        <v>2689</v>
+      </c>
+      <c r="J374" s="4" t="s">
+        <v>2690</v>
+      </c>
+      <c r="K374" s="4" t="s">
+        <v>2691</v>
+      </c>
+      <c r="L374" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="M374" s="4" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13">
+      <c r="A375" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B375" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C375" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>2694</v>
+      </c>
+      <c r="F375" s="4" t="s">
+        <v>2695</v>
+      </c>
+      <c r="G375" s="4" t="s">
+        <v>2696</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>2697</v>
+      </c>
+      <c r="I375" s="4" t="s">
+        <v>2698</v>
+      </c>
+      <c r="J375" s="4" t="s">
+        <v>2699</v>
+      </c>
+      <c r="K375" s="4" t="s">
+        <v>2700</v>
+      </c>
+      <c r="L375" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="M375" s="4" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13">
+      <c r="A376" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C376" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>2702</v>
+      </c>
+      <c r="E376" s="4" t="s">
+        <v>2703</v>
+      </c>
+      <c r="F376" s="4" t="s">
+        <v>2704</v>
+      </c>
+      <c r="G376" s="4" t="s">
+        <v>2705</v>
+      </c>
+      <c r="H376" s="4" t="s">
+        <v>2706</v>
+      </c>
+      <c r="I376" s="4" t="s">
+        <v>2707</v>
+      </c>
+      <c r="J376" s="4" t="s">
+        <v>2708</v>
+      </c>
+      <c r="K376" s="4" t="s">
+        <v>2709</v>
+      </c>
+      <c r="L376" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="M376" s="4" t="s">
+        <v>2710</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13">
+      <c r="A377" s="4" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>2711</v>
+      </c>
+      <c r="E377" s="4" t="s">
+        <v>2712</v>
+      </c>
+      <c r="F377" s="4" t="s">
+        <v>2713</v>
+      </c>
+      <c r="G377" s="4" t="s">
+        <v>2714</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>2715</v>
+      </c>
+      <c r="I377" s="4" t="s">
+        <v>2716</v>
+      </c>
+      <c r="J377" s="4" t="s">
+        <v>2717</v>
+      </c>
+      <c r="K377" s="4" t="s">
+        <v>2718</v>
+      </c>
+      <c r="L377" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="M377" s="4" t="s">
+        <v>2719</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13">
+      <c r="A378" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>2721</v>
+      </c>
+      <c r="E378" s="4" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G378" s="4" t="s">
+        <v>2724</v>
+      </c>
+      <c r="H378" s="4" t="s">
+        <v>2725</v>
+      </c>
+      <c r="I378" s="4" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J378" s="4" t="s">
+        <v>2726</v>
+      </c>
+      <c r="K378" s="4" t="s">
+        <v>2727</v>
+      </c>
+      <c r="L378" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="M378" s="4" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13">
+      <c r="A379" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E379" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F379" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G379" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="H379" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="I379" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J379" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K379" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="L379" s="4" t="s">
+        <v>2729</v>
+      </c>
+      <c r="M379" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13">
+      <c r="A380" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E380" s="4" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F380" s="4" t="s">
+        <v>2732</v>
+      </c>
+      <c r="G380" s="4" t="s">
+        <v>2733</v>
+      </c>
+      <c r="H380" s="4" t="s">
+        <v>2734</v>
+      </c>
+      <c r="I380" s="4" t="s">
+        <v>2735</v>
+      </c>
+      <c r="J380" s="4" t="s">
+        <v>2736</v>
+      </c>
+      <c r="K380" s="4" t="s">
+        <v>2737</v>
+      </c>
+      <c r="L380" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="M380" s="4" t="s">
+        <v>2738</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13">
+      <c r="A381" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E381" s="4" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F381" s="4" t="s">
+        <v>2741</v>
+      </c>
+      <c r="G381" s="4" t="s">
+        <v>2742</v>
+      </c>
+      <c r="H381" s="4" t="s">
+        <v>2743</v>
+      </c>
+      <c r="I381" s="4" t="s">
+        <v>1845</v>
+      </c>
+      <c r="J381" s="4" t="s">
+        <v>2744</v>
+      </c>
+      <c r="K381" s="4" t="s">
+        <v>2745</v>
+      </c>
+      <c r="L381" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="M381" s="4" t="s">
+        <v>2746</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13">
+      <c r="A382" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E382" s="4" t="s">
+        <v>2748</v>
+      </c>
+      <c r="F382" s="4" t="s">
+        <v>2749</v>
+      </c>
+      <c r="G382" s="4" t="s">
+        <v>2750</v>
+      </c>
+      <c r="H382" s="4" t="s">
+        <v>2751</v>
+      </c>
+      <c r="I382" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="J382" s="4" t="s">
+        <v>2752</v>
+      </c>
+      <c r="K382" s="4" t="s">
+        <v>2753</v>
+      </c>
+      <c r="L382" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="M382" s="4" t="s">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13">
+      <c r="A383" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C383" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E383" s="4" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F383" s="4" t="s">
+        <v>2757</v>
+      </c>
+      <c r="G383" s="4" t="s">
+        <v>2758</v>
+      </c>
+      <c r="H383" s="4" t="s">
+        <v>2759</v>
+      </c>
+      <c r="I383" s="4" t="s">
+        <v>1810</v>
+      </c>
+      <c r="J383" s="4" t="s">
+        <v>2760</v>
+      </c>
+      <c r="K383" s="4" t="s">
+        <v>2761</v>
+      </c>
+      <c r="L383" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="M383" s="4" t="s">
+        <v>2762</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13">
+      <c r="A384" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C384" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>2763</v>
+      </c>
+      <c r="E384" s="4" t="s">
+        <v>2764</v>
+      </c>
+      <c r="F384" s="4" t="s">
+        <v>2765</v>
+      </c>
+      <c r="G384" s="4" t="s">
+        <v>2766</v>
+      </c>
+      <c r="H384" s="4" t="s">
+        <v>2767</v>
+      </c>
+      <c r="I384" s="4" t="s">
+        <v>2768</v>
+      </c>
+      <c r="J384" s="4" t="s">
+        <v>2769</v>
+      </c>
+      <c r="K384" s="4" t="s">
+        <v>2770</v>
+      </c>
+      <c r="L384" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="M384" s="4" t="s">
+        <v>2771</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13">
+      <c r="A385" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C385" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>2772</v>
+      </c>
+      <c r="E385" s="4" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F385" s="4" t="s">
+        <v>2774</v>
+      </c>
+      <c r="G385" s="4" t="s">
+        <v>2775</v>
+      </c>
+      <c r="H385" s="4" t="s">
+        <v>2776</v>
+      </c>
+      <c r="I385" s="4" t="s">
+        <v>2777</v>
+      </c>
+      <c r="J385" s="4" t="s">
+        <v>2778</v>
+      </c>
+      <c r="K385" s="4" t="s">
+        <v>2779</v>
+      </c>
+      <c r="L385" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="M385" s="4" t="s">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13">
+      <c r="A386" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B386" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C386" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>2781</v>
+      </c>
+      <c r="E386" s="4" t="s">
+        <v>2782</v>
+      </c>
+      <c r="F386" s="4" t="s">
+        <v>2783</v>
+      </c>
+      <c r="G386" s="4" t="s">
+        <v>2784</v>
+      </c>
+      <c r="H386" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I386" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="J386" s="4" t="s">
+        <v>2785</v>
+      </c>
+      <c r="K386" s="4" t="s">
+        <v>2786</v>
+      </c>
+      <c r="L386" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="M386" s="4" t="s">
+        <v>2787</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13">
+      <c r="A387" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>2788</v>
+      </c>
+      <c r="E387" s="4" t="s">
+        <v>2789</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>2790</v>
+      </c>
+      <c r="G387" s="4" t="s">
+        <v>2791</v>
+      </c>
+      <c r="H387" s="4" t="s">
+        <v>2792</v>
+      </c>
+      <c r="I387" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J387" s="4" t="s">
+        <v>2793</v>
+      </c>
+      <c r="K387" s="4" t="s">
+        <v>2794</v>
+      </c>
+      <c r="L387" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="M387" s="4" t="s">
+        <v>2795</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Z333" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Z352" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="2026-08-07"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="2026-08-07"/>
+      </customFilters>
     </filterColumn>
     <filterColumn colId="1">
-      <filters>
-        <filter val="爆量算法池"/>
-        <filter val="大神"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="爆量算法池"/>
+        <customFilter operator="equal" val="大神"/>
+      </customFilters>
     </filterColumn>
-    <sortState ref="A2:Z333">
+    <sortState ref="A1:Z352">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>

--- a/data/uploads/tongshi_demo.xlsx
+++ b/data/uploads/tongshi_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="11740"/>
+    <workbookView windowWidth="26860" windowHeight="11140"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$Z$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet!$A$1:$Z$405</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4628" uniqueCount="2945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4363" uniqueCount="2703">
   <si>
     <t>日期</t>
   </si>
@@ -8006,865 +8006,139 @@
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>0.00343871</t>
-  </si>
-  <si>
-    <t>302773</t>
-  </si>
-  <si>
-    <t>72120</t>
-  </si>
-  <si>
-    <t>20279</t>
-  </si>
-  <si>
-    <t>14107</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>1879967</t>
-  </si>
-  <si>
-    <t>940101</t>
-  </si>
-  <si>
-    <t>84502</t>
-  </si>
-  <si>
     <t>爆量再植课</t>
   </si>
   <si>
-    <t>0.00560159</t>
-  </si>
-  <si>
-    <t>84915</t>
-  </si>
-  <si>
-    <t>21601</t>
-  </si>
-  <si>
-    <t>6788</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>481789</t>
-  </si>
-  <si>
-    <t>228486</t>
-  </si>
-  <si>
-    <t>24434</t>
-  </si>
-  <si>
-    <t>0.00122588</t>
-  </si>
-  <si>
-    <t>127821</t>
-  </si>
-  <si>
-    <t>34261</t>
-  </si>
-  <si>
-    <t>2523</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>706552</t>
-  </si>
-  <si>
-    <t>125712</t>
-  </si>
-  <si>
-    <t>36748</t>
-  </si>
-  <si>
-    <t>0.00068393</t>
-  </si>
-  <si>
-    <t>827316</t>
-  </si>
-  <si>
-    <t>214934</t>
-  </si>
-  <si>
-    <t>18087</t>
-  </si>
-  <si>
-    <t>15040</t>
-  </si>
-  <si>
-    <t>4533896</t>
-  </si>
-  <si>
-    <t>1061952</t>
-  </si>
-  <si>
-    <t>233544</t>
-  </si>
-  <si>
-    <t>0.00631255</t>
-  </si>
-  <si>
-    <t>142242</t>
-  </si>
-  <si>
-    <t>25980</t>
-  </si>
-  <si>
-    <t>10201</t>
-  </si>
-  <si>
-    <t>6689</t>
-  </si>
-  <si>
-    <t>840225</t>
-  </si>
-  <si>
-    <t>546831</t>
-  </si>
-  <si>
-    <t>33338</t>
-  </si>
-  <si>
-    <t>0.01972494</t>
-  </si>
-  <si>
-    <t>92913</t>
-  </si>
-  <si>
-    <t>34829</t>
-  </si>
-  <si>
-    <t>14822</t>
-  </si>
-  <si>
-    <t>9475</t>
-  </si>
-  <si>
-    <t>687</t>
-  </si>
-  <si>
-    <t>1083922</t>
-  </si>
-  <si>
-    <t>692548</t>
-  </si>
-  <si>
-    <t>43938</t>
-  </si>
-  <si>
-    <t>0.00957354</t>
-  </si>
-  <si>
-    <t>50139</t>
-  </si>
-  <si>
-    <t>8043</t>
-  </si>
-  <si>
-    <t>2608</t>
-  </si>
-  <si>
-    <t>1900</t>
-  </si>
-  <si>
-    <t>333355</t>
-  </si>
-  <si>
-    <t>229435</t>
-  </si>
-  <si>
-    <t>1.47</t>
-  </si>
-  <si>
-    <t>11433</t>
-  </si>
-  <si>
-    <t>0.00185620</t>
-  </si>
-  <si>
-    <t>197669</t>
-  </si>
-  <si>
-    <t>58722</t>
-  </si>
-  <si>
-    <t>3329</t>
-  </si>
-  <si>
-    <t>2876</t>
-  </si>
-  <si>
-    <t>1137826</t>
-  </si>
-  <si>
-    <t>209398</t>
-  </si>
-  <si>
-    <t>62864</t>
-  </si>
-  <si>
-    <t>0.00097628</t>
-  </si>
-  <si>
-    <t>112031</t>
-  </si>
-  <si>
-    <t>24583</t>
-  </si>
-  <si>
-    <t>2464</t>
-  </si>
-  <si>
-    <t>1995</t>
-  </si>
-  <si>
-    <t>547891</t>
-  </si>
-  <si>
-    <t>159631</t>
-  </si>
-  <si>
-    <t>27253</t>
-  </si>
-  <si>
     <t>2026-08-12</t>
   </si>
   <si>
-    <t>0.00237033</t>
-  </si>
-  <si>
-    <t>469498</t>
-  </si>
-  <si>
-    <t>121080</t>
-  </si>
-  <si>
-    <t>25118</t>
-  </si>
-  <si>
-    <t>17983</t>
-  </si>
-  <si>
-    <t>2914903</t>
-  </si>
-  <si>
-    <t>1224658</t>
-  </si>
-  <si>
-    <t>138118</t>
-  </si>
-  <si>
-    <t>0.00087338</t>
-  </si>
-  <si>
-    <t>154217</t>
-  </si>
-  <si>
-    <t>51524</t>
-  </si>
-  <si>
-    <t>3307</t>
-  </si>
-  <si>
-    <t>2801</t>
-  </si>
-  <si>
-    <t>1024172</t>
-  </si>
-  <si>
-    <t>159160</t>
-  </si>
-  <si>
-    <t>54967</t>
-  </si>
-  <si>
-    <t>0.00563181</t>
-  </si>
-  <si>
-    <t>175903</t>
-  </si>
-  <si>
-    <t>35335</t>
-  </si>
-  <si>
-    <t>10831</t>
-  </si>
-  <si>
-    <t>7383</t>
-  </si>
-  <si>
-    <t>1039132</t>
-  </si>
-  <si>
-    <t>604271</t>
-  </si>
-  <si>
-    <t>43659</t>
-  </si>
-  <si>
-    <t>0.00074776</t>
-  </si>
-  <si>
-    <t>743312</t>
-  </si>
-  <si>
-    <t>195249</t>
-  </si>
-  <si>
-    <t>19908</t>
-  </si>
-  <si>
-    <t>16480</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>4240465</t>
-  </si>
-  <si>
-    <t>1163770</t>
-  </si>
-  <si>
-    <t>214580</t>
-  </si>
-  <si>
-    <t>0.00483092</t>
-  </si>
-  <si>
-    <t>205145</t>
-  </si>
-  <si>
-    <t>57960</t>
-  </si>
-  <si>
-    <t>13626</t>
-  </si>
-  <si>
-    <t>9334</t>
-  </si>
-  <si>
-    <t>1254303</t>
-  </si>
-  <si>
-    <t>503013</t>
-  </si>
-  <si>
-    <t>64439</t>
-  </si>
-  <si>
-    <t>0.00193933</t>
-  </si>
-  <si>
-    <t>192864</t>
-  </si>
-  <si>
-    <t>56205</t>
-  </si>
-  <si>
-    <t>2969</t>
-  </si>
-  <si>
-    <t>2582</t>
-  </si>
-  <si>
-    <t>1092150</t>
-  </si>
-  <si>
-    <t>183219</t>
-  </si>
-  <si>
-    <t>59921</t>
-  </si>
-  <si>
-    <t>0.01818534</t>
-  </si>
-  <si>
-    <t>64457</t>
-  </si>
-  <si>
-    <t>20676</t>
-  </si>
-  <si>
-    <t>8093</t>
-  </si>
-  <si>
-    <t>5429</t>
-  </si>
-  <si>
-    <t>633974</t>
-  </si>
-  <si>
-    <t>395182</t>
-  </si>
-  <si>
-    <t>25866</t>
-  </si>
-  <si>
     <t>2026-08-13</t>
   </si>
   <si>
-    <t>0.00309902</t>
-  </si>
-  <si>
-    <t>432305</t>
-  </si>
-  <si>
-    <t>105840</t>
-  </si>
-  <si>
-    <t>26735</t>
-  </si>
-  <si>
-    <t>18736</t>
-  </si>
-  <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>2666715</t>
-  </si>
-  <si>
-    <t>1265835</t>
-  </si>
-  <si>
-    <t>122904</t>
-  </si>
-  <si>
-    <t>0.00092046</t>
-  </si>
-  <si>
-    <t>108689</t>
-  </si>
-  <si>
-    <t>26074</t>
-  </si>
-  <si>
-    <t>1618</t>
-  </si>
-  <si>
-    <t>1380</t>
-  </si>
-  <si>
-    <t>496055</t>
-  </si>
-  <si>
-    <t>87536</t>
-  </si>
-  <si>
-    <t>27761</t>
-  </si>
-  <si>
     <t>爆量未加微</t>
   </si>
   <si>
-    <t>0.00864260</t>
-  </si>
-  <si>
-    <t>3714</t>
-  </si>
-  <si>
-    <t>1967</t>
-  </si>
-  <si>
-    <t>1022</t>
-  </si>
-  <si>
-    <t>846</t>
-  </si>
-  <si>
-    <t>55014</t>
-  </si>
-  <si>
-    <t>34469</t>
-  </si>
-  <si>
-    <t>2320</t>
-  </si>
-  <si>
-    <t>0.00463665</t>
-  </si>
-  <si>
-    <t>293769</t>
-  </si>
-  <si>
-    <t>88426</t>
-  </si>
-  <si>
-    <t>18581</t>
-  </si>
-  <si>
-    <t>12423</t>
-  </si>
-  <si>
-    <t>410</t>
-  </si>
-  <si>
-    <t>1850595</t>
-  </si>
-  <si>
-    <t>726084</t>
-  </si>
-  <si>
-    <t>98052</t>
-  </si>
-  <si>
-    <t>0.00099308</t>
-  </si>
-  <si>
-    <t>566542</t>
-  </si>
-  <si>
-    <t>139968</t>
-  </si>
-  <si>
-    <t>12312</t>
-  </si>
-  <si>
-    <t>10120</t>
-  </si>
-  <si>
-    <t>2981253</t>
-  </si>
-  <si>
-    <t>806093</t>
-  </si>
-  <si>
-    <t>153821</t>
-  </si>
-  <si>
-    <t>0.00676869</t>
-  </si>
-  <si>
-    <t>133262</t>
-  </si>
-  <si>
-    <t>23786</t>
-  </si>
-  <si>
-    <t>8287</t>
-  </si>
-  <si>
-    <t>5686</t>
-  </si>
-  <si>
-    <t>786677</t>
-  </si>
-  <si>
-    <t>507587</t>
-  </si>
-  <si>
-    <t>30838</t>
-  </si>
-  <si>
-    <t>0.04736842</t>
-  </si>
-  <si>
-    <t>1272</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t>324</t>
-  </si>
-  <si>
-    <t>29181</t>
-  </si>
-  <si>
-    <t>22551</t>
-  </si>
-  <si>
-    <t>880</t>
-  </si>
-  <si>
-    <t>0.00123097</t>
-  </si>
-  <si>
-    <t>214475</t>
-  </si>
-  <si>
-    <t>57678</t>
-  </si>
-  <si>
-    <t>3125</t>
-  </si>
-  <si>
-    <t>2734</t>
-  </si>
-  <si>
-    <t>1070946</t>
-  </si>
-  <si>
-    <t>177236</t>
-  </si>
-  <si>
-    <t>61251</t>
-  </si>
-  <si>
-    <t>0.02093259</t>
-  </si>
-  <si>
-    <t>108174</t>
-  </si>
-  <si>
-    <t>32533</t>
-  </si>
-  <si>
-    <t>10981</t>
-  </si>
-  <si>
-    <t>7583</t>
-  </si>
-  <si>
-    <t>681</t>
-  </si>
-  <si>
-    <t>1079653</t>
-  </si>
-  <si>
-    <t>675233</t>
-  </si>
-  <si>
-    <t>42056</t>
-  </si>
-  <si>
     <t>2026-08-14</t>
   </si>
   <si>
-    <t>0.00302144</t>
-  </si>
-  <si>
-    <t>306135</t>
-  </si>
-  <si>
-    <t>82411</t>
-  </si>
-  <si>
-    <t>21555</t>
-  </si>
-  <si>
-    <t>15020</t>
-  </si>
-  <si>
-    <t>2070161</t>
-  </si>
-  <si>
-    <t>977457</t>
-  </si>
-  <si>
-    <t>95302</t>
-  </si>
-  <si>
-    <t>0.00753819</t>
-  </si>
-  <si>
-    <t>9121</t>
-  </si>
-  <si>
-    <t>5041</t>
-  </si>
-  <si>
-    <t>2642</t>
-  </si>
-  <si>
-    <t>2266</t>
-  </si>
-  <si>
-    <t>139075</t>
-  </si>
-  <si>
-    <t>85111</t>
-  </si>
-  <si>
-    <t>5920</t>
-  </si>
-  <si>
-    <t>0.00042283</t>
-  </si>
-  <si>
-    <t>10824</t>
-  </si>
-  <si>
-    <t>4730</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>90696</t>
-  </si>
-  <si>
-    <t>10985</t>
-  </si>
-  <si>
-    <t>4955</t>
-  </si>
-  <si>
-    <t>0.00054963</t>
-  </si>
-  <si>
-    <t>395633</t>
-  </si>
-  <si>
-    <t>174662</t>
-  </si>
-  <si>
-    <t>16153</t>
-  </si>
-  <si>
-    <t>11942</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>3237856</t>
-  </si>
-  <si>
-    <t>747041</t>
-  </si>
-  <si>
-    <t>186072</t>
-  </si>
-  <si>
-    <t>0.00382119</t>
-  </si>
-  <si>
-    <t>175347</t>
-  </si>
-  <si>
-    <t>54695</t>
-  </si>
-  <si>
-    <t>13629</t>
-  </si>
-  <si>
-    <t>9563</t>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>0.02412008</t>
+  </si>
+  <si>
+    <t>57390</t>
+  </si>
+  <si>
+    <t>15257</t>
+  </si>
+  <si>
+    <t>6359</t>
+  </si>
+  <si>
+    <t>4096</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>540797</t>
+  </si>
+  <si>
+    <t>363794</t>
+  </si>
+  <si>
+    <t>20244</t>
+  </si>
+  <si>
+    <t>0.02870813</t>
+  </si>
+  <si>
+    <t>723</t>
   </si>
   <si>
     <t>209</t>
   </si>
   <si>
-    <t>1426802</t>
-  </si>
-  <si>
-    <t>724965</t>
-  </si>
-  <si>
-    <t>64576</t>
-  </si>
-  <si>
-    <t>0.00403922</t>
-  </si>
-  <si>
-    <t>234498</t>
-  </si>
-  <si>
-    <t>71796</t>
-  </si>
-  <si>
-    <t>17069</t>
-  </si>
-  <si>
-    <t>11329</t>
-  </si>
-  <si>
-    <t>1606774</t>
-  </si>
-  <si>
-    <t>629885</t>
-  </si>
-  <si>
-    <t>80231</t>
-  </si>
-  <si>
-    <t>0.04276316</t>
-  </si>
-  <si>
-    <t>1340</t>
-  </si>
-  <si>
-    <t>608</t>
-  </si>
-  <si>
-    <t>319</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>28620</t>
-  </si>
-  <si>
-    <t>21646</t>
-  </si>
-  <si>
-    <t>0.01664840</t>
-  </si>
-  <si>
-    <t>149883</t>
-  </si>
-  <si>
-    <t>38322</t>
-  </si>
-  <si>
-    <t>12502</t>
-  </si>
-  <si>
-    <t>8459</t>
-  </si>
-  <si>
-    <t>638</t>
-  </si>
-  <si>
-    <t>1152561</t>
-  </si>
-  <si>
-    <t>676891</t>
-  </si>
-  <si>
-    <t>47684</t>
-  </si>
-  <si>
-    <t>0.00151175</t>
-  </si>
-  <si>
-    <t>200339</t>
-  </si>
-  <si>
-    <t>65487</t>
-  </si>
-  <si>
-    <t>3961</t>
-  </si>
-  <si>
-    <t>3403</t>
-  </si>
-  <si>
-    <t>1273651</t>
-  </si>
-  <si>
-    <t>216996</t>
-  </si>
-  <si>
-    <t>70089</t>
-  </si>
-  <si>
-    <t>0.03</t>
+    <t>11821</t>
+  </si>
+  <si>
+    <t>9183</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>0.00107506</t>
+  </si>
+  <si>
+    <t>568821</t>
+  </si>
+  <si>
+    <t>110691</t>
+  </si>
+  <si>
+    <t>14010</t>
+  </si>
+  <si>
+    <t>10249</t>
+  </si>
+  <si>
+    <t>2339104</t>
+  </si>
+  <si>
+    <t>716466</t>
+  </si>
+  <si>
+    <t>121561</t>
+  </si>
+  <si>
+    <t>0.00468854</t>
+  </si>
+  <si>
+    <t>265049</t>
+  </si>
+  <si>
+    <t>63346</t>
+  </si>
+  <si>
+    <t>18658</t>
+  </si>
+  <si>
+    <t>11911</t>
+  </si>
+  <si>
+    <t>1453700</t>
+  </si>
+  <si>
+    <t>626320</t>
+  </si>
+  <si>
+    <t>71327</t>
+  </si>
+  <si>
+    <t>0.01753036</t>
+  </si>
+  <si>
+    <t>141432</t>
+  </si>
+  <si>
+    <t>35082</t>
+  </si>
+  <si>
+    <t>13345</t>
+  </si>
+  <si>
+    <t>1099283</t>
+  </si>
+  <si>
+    <t>675376</t>
+  </si>
+  <si>
+    <t>44282</t>
   </si>
 </sst>
 </file>
@@ -8894,14 +8168,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -9896,14 +9170,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Z396"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:Z407"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.0192307692308" style="1" customWidth="1"/>
     <col min="2" max="3" width="18.1057692307692" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.4134615384615" style="1" customWidth="1"/>
-    <col min="5" max="13" width="9" style="1"/>
+    <col min="5" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="12.3365384615385" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7692307692308" style="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="12.9230769230769" style="1"/>
+    <col min="12" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="13.4615384615385" style="1" customWidth="1"/>
     <col min="14" max="14" width="12.9230769230769"/>
     <col min="17" max="17" width="12.9230769230769"/>
     <col min="22" max="22" width="12.9230769230769"/>
@@ -9950,7 +9230,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" hidden="1" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -9991,7 +9271,7 @@
         <v>72312</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" hidden="1" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -10032,7 +9312,7 @@
         <v>89771</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" hidden="1" spans="1:13">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -10073,7 +9353,7 @@
         <v>34193</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" hidden="1" spans="1:13">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -10114,7 +9394,7 @@
         <v>26096</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" hidden="1" spans="1:13">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -10155,7 +9435,7 @@
         <v>108005</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" hidden="1" spans="1:13">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -10196,7 +9476,7 @@
         <v>63288</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" hidden="1" spans="1:13">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -10237,7 +9517,7 @@
         <v>23977</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" hidden="1" spans="1:13">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
@@ -10278,7 +9558,7 @@
         <v>40416</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" hidden="1" spans="1:13">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -10319,7 +9599,7 @@
         <v>27054</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" hidden="1" spans="1:13">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -10360,7 +9640,7 @@
         <v>75769</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" hidden="1" spans="1:13">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -10401,7 +9681,7 @@
         <v>41004</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" hidden="1" spans="1:13">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
@@ -10442,7 +9722,7 @@
         <v>7566</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" hidden="1" spans="1:13">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -10483,7 +9763,7 @@
         <v>137509</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" hidden="1" spans="1:13">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -10524,7 +9804,7 @@
         <v>9465</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" hidden="1" spans="1:13">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -10565,7 +9845,7 @@
         <v>34392</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" hidden="1" spans="1:13">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
@@ -10606,7 +9886,7 @@
         <v>27039</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" hidden="1" spans="1:13">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -10647,7 +9927,7 @@
         <v>8316</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" hidden="1" spans="1:13">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -10688,7 +9968,7 @@
         <v>38256</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" hidden="1" spans="1:13">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -10729,7 +10009,7 @@
         <v>16105</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" hidden="1" spans="1:13">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
@@ -10770,7 +10050,7 @@
         <v>84767</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" hidden="1" spans="1:13">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -10811,7 +10091,7 @@
         <v>83420</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" hidden="1" spans="1:13">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -10852,7 +10132,7 @@
         <v>17377</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" hidden="1" spans="1:13">
       <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
@@ -10893,7 +10173,7 @@
         <v>9594</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" hidden="1" spans="1:13">
       <c r="A25" s="2" t="s">
         <v>22</v>
       </c>
@@ -10934,7 +10214,7 @@
         <v>10652</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" hidden="1" spans="1:13">
       <c r="A26" s="2" t="s">
         <v>22</v>
       </c>
@@ -10975,7 +10255,7 @@
         <v>23160</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" hidden="1" spans="1:13">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -11016,7 +10296,7 @@
         <v>162769</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" hidden="1" spans="1:13">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
@@ -11057,7 +10337,7 @@
         <v>36111</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" hidden="1" spans="1:13">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -11098,7 +10378,7 @@
         <v>5286</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" hidden="1" spans="1:13">
       <c r="A30" s="2" t="s">
         <v>22</v>
       </c>
@@ -11139,7 +10419,7 @@
         <v>20887</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" hidden="1" spans="1:13">
       <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
@@ -11180,7 +10460,7 @@
         <v>89918</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" hidden="1" spans="1:13">
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
@@ -11221,7 +10501,7 @@
         <v>26228</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" hidden="1" spans="1:13">
       <c r="A33" s="2" t="s">
         <v>23</v>
       </c>
@@ -11262,7 +10542,7 @@
         <v>22487</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" hidden="1" spans="1:13">
       <c r="A34" s="2" t="s">
         <v>23</v>
       </c>
@@ -11303,7 +10583,7 @@
         <v>72972</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" hidden="1" spans="1:13">
       <c r="A35" s="2" t="s">
         <v>23</v>
       </c>
@@ -11344,7 +10624,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" hidden="1" spans="1:13">
       <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
@@ -11385,7 +10665,7 @@
         <v>48778</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" hidden="1" spans="1:13">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
@@ -11426,7 +10706,7 @@
         <v>7331</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" hidden="1" spans="1:13">
       <c r="A38" s="2" t="s">
         <v>23</v>
       </c>
@@ -11467,7 +10747,7 @@
         <v>20308</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" hidden="1" spans="1:13">
       <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
@@ -11508,7 +10788,7 @@
         <v>206657</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" hidden="1" spans="1:13">
       <c r="A40" s="2" t="s">
         <v>23</v>
       </c>
@@ -11549,7 +10829,7 @@
         <v>44060</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" hidden="1" spans="1:13">
       <c r="A41" s="2" t="s">
         <v>23</v>
       </c>
@@ -11590,7 +10870,7 @@
         <v>37551</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" hidden="1" spans="1:13">
       <c r="A42" s="2" t="s">
         <v>23</v>
       </c>
@@ -11631,7 +10911,7 @@
         <v>10158</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" hidden="1" spans="1:13">
       <c r="A43" s="2" t="s">
         <v>23</v>
       </c>
@@ -11672,7 +10952,7 @@
         <v>12556</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" hidden="1" spans="1:13">
       <c r="A44" s="2" t="s">
         <v>24</v>
       </c>
@@ -11709,7 +10989,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" hidden="1" spans="1:13">
       <c r="A45" s="2" t="s">
         <v>24</v>
       </c>
@@ -11750,7 +11030,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" hidden="1" spans="1:13">
       <c r="A46" s="2" t="s">
         <v>24</v>
       </c>
@@ -11791,7 +11071,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" hidden="1" spans="1:13">
       <c r="A47" s="2" t="s">
         <v>24</v>
       </c>
@@ -11832,7 +11112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" hidden="1" spans="1:13">
       <c r="A48" s="2" t="s">
         <v>24</v>
       </c>
@@ -11873,7 +11153,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" hidden="1" spans="1:13">
       <c r="A49" s="2" t="s">
         <v>24</v>
       </c>
@@ -11914,7 +11194,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" hidden="1" spans="1:13">
       <c r="A50" s="2" t="s">
         <v>24</v>
       </c>
@@ -11955,7 +11235,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" hidden="1" spans="1:13">
       <c r="A51" s="2" t="s">
         <v>24</v>
       </c>
@@ -11996,7 +11276,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" hidden="1" spans="1:13">
       <c r="A52" s="2" t="s">
         <v>24</v>
       </c>
@@ -12037,7 +11317,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" hidden="1" spans="1:13">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -12078,7 +11358,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" hidden="1" spans="1:13">
       <c r="A54" s="2" t="s">
         <v>24</v>
       </c>
@@ -12119,7 +11399,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" hidden="1" spans="1:13">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -12160,7 +11440,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" hidden="1" spans="1:13">
       <c r="A56" s="2" t="s">
         <v>136</v>
       </c>
@@ -12201,7 +11481,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" hidden="1" spans="1:13">
       <c r="A57" s="2" t="s">
         <v>136</v>
       </c>
@@ -12242,7 +11522,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" hidden="1" spans="1:13">
       <c r="A58" s="2" t="s">
         <v>136</v>
       </c>
@@ -12283,7 +11563,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" hidden="1" spans="1:13">
       <c r="A59" s="2" t="s">
         <v>162</v>
       </c>
@@ -12324,7 +11604,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" hidden="1" spans="1:13">
       <c r="A60" s="2" t="s">
         <v>162</v>
       </c>
@@ -12365,7 +11645,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" hidden="1" spans="1:13">
       <c r="A61" s="2" t="s">
         <v>162</v>
       </c>
@@ -12406,7 +11686,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" hidden="1" spans="1:13">
       <c r="A62" s="2" t="s">
         <v>162</v>
       </c>
@@ -12447,7 +11727,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" hidden="1" spans="1:13">
       <c r="A63" s="2" t="s">
         <v>162</v>
       </c>
@@ -12488,7 +11768,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" hidden="1" spans="1:13">
       <c r="A64" s="2" t="s">
         <v>162</v>
       </c>
@@ -12529,7 +11809,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" hidden="1" spans="1:13">
       <c r="A65" s="2" t="s">
         <v>162</v>
       </c>
@@ -12570,7 +11850,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" hidden="1" spans="1:13">
       <c r="A66" s="2" t="s">
         <v>162</v>
       </c>
@@ -12611,7 +11891,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" hidden="1" spans="1:13">
       <c r="A67" s="2" t="s">
         <v>162</v>
       </c>
@@ -12652,7 +11932,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" hidden="1" spans="1:13">
       <c r="A68" s="2" t="s">
         <v>162</v>
       </c>
@@ -12693,7 +11973,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" hidden="1" spans="1:13">
       <c r="A69" s="2" t="s">
         <v>259</v>
       </c>
@@ -12734,7 +12014,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" hidden="1" spans="1:13">
       <c r="A70" s="2" t="s">
         <v>259</v>
       </c>
@@ -12775,7 +12055,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" hidden="1" spans="1:13">
       <c r="A71" s="2" t="s">
         <v>259</v>
       </c>
@@ -12816,7 +12096,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" hidden="1" spans="1:13">
       <c r="A72" s="2" t="s">
         <v>259</v>
       </c>
@@ -12857,7 +12137,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" hidden="1" spans="1:13">
       <c r="A73" s="2" t="s">
         <v>259</v>
       </c>
@@ -12898,7 +12178,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" hidden="1" spans="1:13">
       <c r="A74" s="2" t="s">
         <v>259</v>
       </c>
@@ -12939,7 +12219,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" hidden="1" spans="1:13">
       <c r="A75" s="2" t="s">
         <v>259</v>
       </c>
@@ -12980,7 +12260,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" hidden="1" spans="1:13">
       <c r="A76" s="2" t="s">
         <v>259</v>
       </c>
@@ -13021,7 +12301,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" hidden="1" spans="1:13">
       <c r="A77" s="2" t="s">
         <v>259</v>
       </c>
@@ -13062,7 +12342,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" hidden="1" spans="1:13">
       <c r="A78" s="2" t="s">
         <v>259</v>
       </c>
@@ -13103,7 +12383,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" hidden="1" spans="1:13">
       <c r="A79" s="2" t="s">
         <v>352</v>
       </c>
@@ -13144,7 +12424,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" hidden="1" spans="1:13">
       <c r="A80" s="2" t="s">
         <v>352</v>
       </c>
@@ -13185,7 +12465,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" hidden="1" spans="1:13">
       <c r="A81" s="2" t="s">
         <v>352</v>
       </c>
@@ -13226,7 +12506,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" hidden="1" spans="1:13">
       <c r="A82" s="2" t="s">
         <v>352</v>
       </c>
@@ -13267,7 +12547,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" hidden="1" spans="1:13">
       <c r="A83" s="2" t="s">
         <v>352</v>
       </c>
@@ -13308,7 +12588,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" hidden="1" spans="1:13">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -13349,7 +12629,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" hidden="1" spans="1:13">
       <c r="A85" s="2" t="s">
         <v>352</v>
       </c>
@@ -13390,7 +12670,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" hidden="1" spans="1:13">
       <c r="A86" s="2" t="s">
         <v>352</v>
       </c>
@@ -13431,7 +12711,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" hidden="1" spans="1:13">
       <c r="A87" s="2" t="s">
         <v>352</v>
       </c>
@@ -13472,7 +12752,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" hidden="1" spans="1:13">
       <c r="A88" s="2" t="s">
         <v>352</v>
       </c>
@@ -13513,7 +12793,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" hidden="1" spans="1:13">
       <c r="A89" s="2" t="s">
         <v>439</v>
       </c>
@@ -13554,7 +12834,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" hidden="1" spans="1:13">
       <c r="A90" s="2" t="s">
         <v>439</v>
       </c>
@@ -13595,7 +12875,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" hidden="1" spans="1:13">
       <c r="A91" s="2" t="s">
         <v>439</v>
       </c>
@@ -13636,7 +12916,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" hidden="1" spans="1:13">
       <c r="A92" s="2" t="s">
         <v>439</v>
       </c>
@@ -13677,7 +12957,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" hidden="1" spans="1:13">
       <c r="A93" s="2" t="s">
         <v>439</v>
       </c>
@@ -13718,7 +12998,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" hidden="1" spans="1:13">
       <c r="A94" s="2" t="s">
         <v>439</v>
       </c>
@@ -13759,7 +13039,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" hidden="1" spans="1:13">
       <c r="A95" s="2" t="s">
         <v>439</v>
       </c>
@@ -13800,7 +13080,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" hidden="1" spans="1:13">
       <c r="A96" s="2" t="s">
         <v>439</v>
       </c>
@@ -13841,7 +13121,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" hidden="1" spans="1:13">
       <c r="A97" s="2" t="s">
         <v>439</v>
       </c>
@@ -13882,7 +13162,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" hidden="1" spans="1:13">
       <c r="A98" s="2" t="s">
         <v>439</v>
       </c>
@@ -13923,7 +13203,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" hidden="1" spans="1:13">
       <c r="A99" s="2" t="s">
         <v>527</v>
       </c>
@@ -13964,7 +13244,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" hidden="1" spans="1:13">
       <c r="A100" s="2" t="s">
         <v>527</v>
       </c>
@@ -14003,7 +13283,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" hidden="1" spans="1:13">
       <c r="A101" s="2" t="s">
         <v>527</v>
       </c>
@@ -14044,7 +13324,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" hidden="1" spans="1:13">
       <c r="A102" s="2" t="s">
         <v>527</v>
       </c>
@@ -14085,7 +13365,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" hidden="1" spans="1:13">
       <c r="A103" s="2" t="s">
         <v>527</v>
       </c>
@@ -14126,7 +13406,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" hidden="1" spans="1:13">
       <c r="A104" s="2" t="s">
         <v>527</v>
       </c>
@@ -14167,7 +13447,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" hidden="1" spans="1:13">
       <c r="A105" s="2" t="s">
         <v>527</v>
       </c>
@@ -14208,7 +13488,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" hidden="1" spans="1:13">
       <c r="A106" s="2" t="s">
         <v>527</v>
       </c>
@@ -14249,7 +13529,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" hidden="1" spans="1:13">
       <c r="A107" s="2" t="s">
         <v>527</v>
       </c>
@@ -14290,7 +13570,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" hidden="1" spans="1:13">
       <c r="A108" s="2" t="s">
         <v>527</v>
       </c>
@@ -14331,7 +13611,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" hidden="1" spans="1:13">
       <c r="A109" s="2" t="s">
         <v>617</v>
       </c>
@@ -14372,7 +13652,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" hidden="1" spans="1:13">
       <c r="A110" s="2" t="s">
         <v>617</v>
       </c>
@@ -14413,7 +13693,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" hidden="1" spans="1:13">
       <c r="A111" s="2" t="s">
         <v>617</v>
       </c>
@@ -14454,7 +13734,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" hidden="1" spans="1:13">
       <c r="A112" s="2" t="s">
         <v>617</v>
       </c>
@@ -14495,7 +13775,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" hidden="1" spans="1:13">
       <c r="A113" s="2" t="s">
         <v>617</v>
       </c>
@@ -14536,7 +13816,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" hidden="1" spans="1:13">
       <c r="A114" s="2" t="s">
         <v>617</v>
       </c>
@@ -14577,7 +13857,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" hidden="1" spans="1:13">
       <c r="A115" s="2" t="s">
         <v>617</v>
       </c>
@@ -14618,7 +13898,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" hidden="1" spans="1:13">
       <c r="A116" s="2" t="s">
         <v>617</v>
       </c>
@@ -14659,7 +13939,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" hidden="1" spans="1:13">
       <c r="A117" s="2" t="s">
         <v>617</v>
       </c>
@@ -14700,7 +13980,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" hidden="1" spans="1:13">
       <c r="A118" s="2" t="s">
         <v>617</v>
       </c>
@@ -14741,7 +14021,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" hidden="1" spans="1:13">
       <c r="A119" s="2" t="s">
         <v>617</v>
       </c>
@@ -14782,7 +14062,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" hidden="1" spans="1:13">
       <c r="A120" s="2" t="s">
         <v>714</v>
       </c>
@@ -14823,7 +14103,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" hidden="1" spans="1:13">
       <c r="A121" s="2" t="s">
         <v>714</v>
       </c>
@@ -14864,7 +14144,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" hidden="1" spans="1:13">
       <c r="A122" s="2" t="s">
         <v>714</v>
       </c>
@@ -14905,7 +14185,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" hidden="1" spans="1:13">
       <c r="A123" s="2" t="s">
         <v>743</v>
       </c>
@@ -14944,7 +14224,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" hidden="1" spans="1:13">
       <c r="A124" s="2" t="s">
         <v>743</v>
       </c>
@@ -14985,7 +14265,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" hidden="1" spans="1:13">
       <c r="A125" s="2" t="s">
         <v>743</v>
       </c>
@@ -15026,7 +14306,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" hidden="1" spans="1:13">
       <c r="A126" s="2" t="s">
         <v>743</v>
       </c>
@@ -15067,7 +14347,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" hidden="1" spans="1:13">
       <c r="A127" s="2" t="s">
         <v>743</v>
       </c>
@@ -15108,7 +14388,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" hidden="1" spans="1:13">
       <c r="A128" s="2" t="s">
         <v>743</v>
       </c>
@@ -15149,7 +14429,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" hidden="1" spans="1:13">
       <c r="A129" s="2" t="s">
         <v>743</v>
       </c>
@@ -15190,7 +14470,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" hidden="1" spans="1:13">
       <c r="A130" s="2" t="s">
         <v>743</v>
       </c>
@@ -15231,7 +14511,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" hidden="1" spans="1:13">
       <c r="A131" s="2" t="s">
         <v>743</v>
       </c>
@@ -15272,7 +14552,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" hidden="1" spans="1:13">
       <c r="A132" s="2" t="s">
         <v>743</v>
       </c>
@@ -15313,7 +14593,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" hidden="1" spans="1:13">
       <c r="A133" s="2" t="s">
         <v>743</v>
       </c>
@@ -15354,7 +14634,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" hidden="1" spans="1:13">
       <c r="A134" s="2" t="s">
         <v>827</v>
       </c>
@@ -15395,7 +14675,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" hidden="1" spans="1:13">
       <c r="A135" s="2" t="s">
         <v>827</v>
       </c>
@@ -15434,7 +14714,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" hidden="1" spans="1:13">
       <c r="A136" s="2" t="s">
         <v>827</v>
       </c>
@@ -15475,7 +14755,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" hidden="1" spans="1:13">
       <c r="A137" s="2" t="s">
         <v>827</v>
       </c>
@@ -15516,7 +14796,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" hidden="1" spans="1:13">
       <c r="A138" s="2" t="s">
         <v>827</v>
       </c>
@@ -15557,7 +14837,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" hidden="1" spans="1:13">
       <c r="A139" s="2" t="s">
         <v>827</v>
       </c>
@@ -15598,7 +14878,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" hidden="1" spans="1:13">
       <c r="A140" s="2" t="s">
         <v>827</v>
       </c>
@@ -15639,7 +14919,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" hidden="1" spans="1:13">
       <c r="A141" s="2" t="s">
         <v>827</v>
       </c>
@@ -15680,7 +14960,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" hidden="1" spans="1:13">
       <c r="A142" s="2" t="s">
         <v>827</v>
       </c>
@@ -15721,7 +15001,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" hidden="1" spans="1:13">
       <c r="A143" s="2" t="s">
         <v>902</v>
       </c>
@@ -15758,7 +15038,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" hidden="1" spans="1:13">
       <c r="A144" s="2" t="s">
         <v>902</v>
       </c>
@@ -15799,7 +15079,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="145" spans="1:26">
+    <row r="145" hidden="1" spans="1:26">
       <c r="A145" s="2" t="s">
         <v>902</v>
       </c>
@@ -15840,7 +15120,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="146" spans="1:26">
+    <row r="146" hidden="1" spans="1:26">
       <c r="A146" s="2" t="s">
         <v>902</v>
       </c>
@@ -15881,7 +15161,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="147" spans="1:26">
+    <row r="147" hidden="1" spans="1:26">
       <c r="A147" s="2" t="s">
         <v>902</v>
       </c>
@@ -15922,7 +15202,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="148" spans="1:26">
+    <row r="148" hidden="1" spans="1:26">
       <c r="A148" s="2" t="s">
         <v>902</v>
       </c>
@@ -15963,7 +15243,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="149" spans="1:26">
+    <row r="149" hidden="1" spans="1:26">
       <c r="A149" s="2" t="s">
         <v>902</v>
       </c>
@@ -16004,7 +15284,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="150" spans="1:26">
+    <row r="150" hidden="1" spans="1:26">
       <c r="A150" s="2" t="s">
         <v>902</v>
       </c>
@@ -16045,7 +15325,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="151" spans="1:26">
+    <row r="151" hidden="1" spans="1:26">
       <c r="A151" s="2" t="s">
         <v>902</v>
       </c>
@@ -16086,7 +15366,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="152" spans="1:26">
+    <row r="152" hidden="1" spans="1:26">
       <c r="A152" s="2" t="s">
         <v>902</v>
       </c>
@@ -16127,7 +15407,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="153" spans="1:26">
+    <row r="153" hidden="1" spans="1:26">
       <c r="A153" s="2" t="s">
         <v>983</v>
       </c>
@@ -16168,7 +15448,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="154" spans="1:26">
+    <row r="154" hidden="1" spans="1:26">
       <c r="A154" s="2" t="s">
         <v>983</v>
       </c>
@@ -16209,7 +15489,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="155" spans="1:26">
+    <row r="155" hidden="1" spans="1:26">
       <c r="A155" s="2" t="s">
         <v>983</v>
       </c>
@@ -16250,7 +15530,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="156" spans="1:26">
+    <row r="156" hidden="1" spans="1:26">
       <c r="A156" s="2" t="s">
         <v>983</v>
       </c>
@@ -16291,7 +15571,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="157" spans="1:26">
+    <row r="157" hidden="1" spans="1:26">
       <c r="A157" s="2" t="s">
         <v>983</v>
       </c>
@@ -16335,7 +15615,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="158" spans="1:26">
+    <row r="158" hidden="1" spans="1:26">
       <c r="A158" s="2" t="s">
         <v>983</v>
       </c>
@@ -16376,7 +15656,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="159" spans="1:26">
+    <row r="159" hidden="1" spans="1:26">
       <c r="A159" s="2" t="s">
         <v>983</v>
       </c>
@@ -16417,7 +15697,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="160" spans="1:26">
+    <row r="160" hidden="1" spans="1:26">
       <c r="A160" s="2" t="s">
         <v>983</v>
       </c>
@@ -16458,7 +15738,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" hidden="1" spans="1:13">
       <c r="A161" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16499,7 +15779,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" hidden="1" spans="1:13">
       <c r="A162" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16540,7 +15820,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" hidden="1" spans="1:13">
       <c r="A163" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16581,7 +15861,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" hidden="1" spans="1:13">
       <c r="A164" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16622,7 +15902,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" hidden="1" spans="1:13">
       <c r="A165" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16663,7 +15943,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" hidden="1" spans="1:13">
       <c r="A166" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16704,7 +15984,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" hidden="1" spans="1:13">
       <c r="A167" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16745,7 +16025,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" hidden="1" spans="1:13">
       <c r="A168" s="2" t="s">
         <v>1057</v>
       </c>
@@ -16786,7 +16066,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" hidden="1" spans="1:13">
       <c r="A169" s="2" t="s">
         <v>1132</v>
       </c>
@@ -16827,7 +16107,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" hidden="1" spans="1:13">
       <c r="A170" s="2" t="s">
         <v>1132</v>
       </c>
@@ -16868,7 +16148,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" hidden="1" spans="1:13">
       <c r="A171" s="2" t="s">
         <v>1132</v>
       </c>
@@ -16909,7 +16189,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" hidden="1" spans="1:13">
       <c r="A172" s="2" t="s">
         <v>1132</v>
       </c>
@@ -16950,7 +16230,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" hidden="1" spans="1:13">
       <c r="A173" s="2" t="s">
         <v>1132</v>
       </c>
@@ -16991,7 +16271,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" hidden="1" spans="1:13">
       <c r="A174" s="2" t="s">
         <v>1132</v>
       </c>
@@ -17032,7 +16312,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" hidden="1" spans="1:13">
       <c r="A175" s="2" t="s">
         <v>1132</v>
       </c>
@@ -17073,7 +16353,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" hidden="1" spans="1:13">
       <c r="A176" s="2" t="s">
         <v>1132</v>
       </c>
@@ -17114,7 +16394,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" hidden="1" spans="1:13">
       <c r="A177" s="2" t="s">
         <v>1205</v>
       </c>
@@ -17155,7 +16435,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" hidden="1" spans="1:13">
       <c r="A178" s="2" t="s">
         <v>1205</v>
       </c>
@@ -17196,7 +16476,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" hidden="1" spans="1:13">
       <c r="A179" s="2" t="s">
         <v>1205</v>
       </c>
@@ -17235,7 +16515,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" hidden="1" spans="1:13">
       <c r="A180" s="2" t="s">
         <v>1205</v>
       </c>
@@ -17276,7 +16556,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" hidden="1" spans="1:13">
       <c r="A181" s="2" t="s">
         <v>1205</v>
       </c>
@@ -17317,7 +16597,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" hidden="1" spans="1:13">
       <c r="A182" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17358,7 +16638,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" hidden="1" spans="1:13">
       <c r="A183" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17399,7 +16679,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" hidden="1" spans="1:13">
       <c r="A184" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17440,7 +16720,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" hidden="1" spans="1:13">
       <c r="A185" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17481,7 +16761,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" hidden="1" spans="1:13">
       <c r="A186" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17522,7 +16802,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" hidden="1" spans="1:13">
       <c r="A187" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17563,7 +16843,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" hidden="1" spans="1:13">
       <c r="A188" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17604,7 +16884,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" hidden="1" spans="1:13">
       <c r="A189" s="2" t="s">
         <v>1232</v>
       </c>
@@ -17645,7 +16925,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" hidden="1" spans="1:13">
       <c r="A190" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17686,7 +16966,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" hidden="1" spans="1:13">
       <c r="A191" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17727,7 +17007,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" hidden="1" spans="1:13">
       <c r="A192" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17768,7 +17048,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" hidden="1" spans="1:13">
       <c r="A193" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17809,7 +17089,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" hidden="1" spans="1:13">
       <c r="A194" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17850,7 +17130,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" hidden="1" spans="1:13">
       <c r="A195" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17891,7 +17171,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" hidden="1" spans="1:13">
       <c r="A196" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17932,7 +17212,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" hidden="1" spans="1:13">
       <c r="A197" s="2" t="s">
         <v>1307</v>
       </c>
@@ -17973,7 +17253,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" hidden="1" spans="1:13">
       <c r="A198" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18014,7 +17294,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" hidden="1" spans="1:13">
       <c r="A199" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18055,7 +17335,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" hidden="1" spans="1:13">
       <c r="A200" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18096,7 +17376,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" hidden="1" spans="1:13">
       <c r="A201" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18137,7 +17417,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" hidden="1" spans="1:13">
       <c r="A202" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18178,7 +17458,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" hidden="1" spans="1:13">
       <c r="A203" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18219,7 +17499,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" hidden="1" spans="1:13">
       <c r="A204" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18260,7 +17540,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" hidden="1" spans="1:13">
       <c r="A205" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18301,7 +17581,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" hidden="1" spans="1:13">
       <c r="A206" s="2" t="s">
         <v>1376</v>
       </c>
@@ -18342,7 +17622,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" hidden="1" spans="1:13">
       <c r="A207" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18383,7 +17663,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" hidden="1" spans="1:13">
       <c r="A208" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18424,7 +17704,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" hidden="1" spans="1:13">
       <c r="A209" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18465,7 +17745,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" hidden="1" spans="1:13">
       <c r="A210" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18506,7 +17786,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" hidden="1" spans="1:13">
       <c r="A211" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18547,7 +17827,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" hidden="1" spans="1:13">
       <c r="A212" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18588,7 +17868,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" hidden="1" spans="1:13">
       <c r="A213" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18629,7 +17909,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" hidden="1" spans="1:13">
       <c r="A214" s="2" t="s">
         <v>1456</v>
       </c>
@@ -18670,7 +17950,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" hidden="1" spans="1:13">
       <c r="A215" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18711,7 +17991,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" hidden="1" spans="1:13">
       <c r="A216" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18752,7 +18032,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" hidden="1" spans="1:13">
       <c r="A217" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18793,7 +18073,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" hidden="1" spans="1:13">
       <c r="A218" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18834,7 +18114,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" hidden="1" spans="1:13">
       <c r="A219" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18875,7 +18155,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" hidden="1" spans="1:13">
       <c r="A220" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18916,7 +18196,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" hidden="1" spans="1:13">
       <c r="A221" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18957,7 +18237,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" hidden="1" spans="1:13">
       <c r="A222" s="2" t="s">
         <v>1528</v>
       </c>
@@ -18998,7 +18278,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" hidden="1" spans="1:13">
       <c r="A223" s="2" t="s">
         <v>1528</v>
       </c>
@@ -19039,7 +18319,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" hidden="1" spans="1:13">
       <c r="A224" s="2" t="s">
         <v>1528</v>
       </c>
@@ -19080,7 +18360,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" hidden="1" spans="1:13">
       <c r="A225" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19121,7 +18401,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" hidden="1" spans="1:13">
       <c r="A226" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19162,7 +18442,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" hidden="1" spans="1:13">
       <c r="A227" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19203,7 +18483,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" hidden="1" spans="1:13">
       <c r="A228" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19244,7 +18524,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" hidden="1" spans="1:13">
       <c r="A229" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19285,7 +18565,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" hidden="1" spans="1:13">
       <c r="A230" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19326,7 +18606,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" hidden="1" spans="1:13">
       <c r="A231" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19367,7 +18647,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" hidden="1" spans="1:13">
       <c r="A232" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19408,7 +18688,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" hidden="1" spans="1:13">
       <c r="A233" s="2" t="s">
         <v>1612</v>
       </c>
@@ -19449,7 +18729,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" hidden="1" spans="1:13">
       <c r="A234" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19490,7 +18770,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" hidden="1" spans="1:13">
       <c r="A235" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19531,7 +18811,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" hidden="1" spans="1:13">
       <c r="A236" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19572,7 +18852,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" hidden="1" spans="1:13">
       <c r="A237" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19613,7 +18893,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" hidden="1" spans="1:13">
       <c r="A238" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19654,7 +18934,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" hidden="1" spans="1:13">
       <c r="A239" s="2" t="s">
         <v>1685</v>
       </c>
@@ -19695,7 +18975,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" hidden="1" spans="1:13">
       <c r="A240" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19736,7 +19016,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" hidden="1" spans="1:13">
       <c r="A241" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19777,7 +19057,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" hidden="1" spans="1:13">
       <c r="A242" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19818,7 +19098,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" hidden="1" spans="1:13">
       <c r="A243" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19859,7 +19139,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" hidden="1" spans="1:13">
       <c r="A244" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19900,7 +19180,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" hidden="1" spans="1:13">
       <c r="A245" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19941,7 +19221,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" hidden="1" spans="1:13">
       <c r="A246" s="2" t="s">
         <v>1730</v>
       </c>
@@ -19982,7 +19262,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" hidden="1" spans="1:13">
       <c r="A247" s="2" t="s">
         <v>1730</v>
       </c>
@@ -20023,7 +19303,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" hidden="1" spans="1:13">
       <c r="A248" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20064,7 +19344,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" hidden="1" spans="1:13">
       <c r="A249" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20105,7 +19385,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" hidden="1" spans="1:13">
       <c r="A250" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20146,7 +19426,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" hidden="1" spans="1:13">
       <c r="A251" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20187,7 +19467,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" hidden="1" spans="1:13">
       <c r="A252" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20228,7 +19508,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" hidden="1" spans="1:13">
       <c r="A253" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20269,7 +19549,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" hidden="1" spans="1:13">
       <c r="A254" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20310,7 +19590,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" hidden="1" spans="1:13">
       <c r="A255" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20351,7 +19631,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" hidden="1" spans="1:13">
       <c r="A256" s="2" t="s">
         <v>1801</v>
       </c>
@@ -20392,7 +19672,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" hidden="1" spans="1:13">
       <c r="A257" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20433,7 +19713,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" hidden="1" spans="1:13">
       <c r="A258" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20474,7 +19754,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" hidden="1" spans="1:13">
       <c r="A259" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20515,7 +19795,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" hidden="1" spans="1:13">
       <c r="A260" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20556,7 +19836,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" hidden="1" spans="1:13">
       <c r="A261" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20597,7 +19877,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" hidden="1" spans="1:13">
       <c r="A262" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20638,7 +19918,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" hidden="1" spans="1:13">
       <c r="A263" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20679,7 +19959,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" hidden="1" spans="1:13">
       <c r="A264" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20720,7 +20000,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" hidden="1" spans="1:13">
       <c r="A265" s="2" t="s">
         <v>1874</v>
       </c>
@@ -20761,7 +20041,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" hidden="1" spans="1:13">
       <c r="A266" s="2" t="s">
         <v>1954</v>
       </c>
@@ -20802,7 +20082,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" hidden="1" spans="1:13">
       <c r="A267" s="2" t="s">
         <v>1954</v>
       </c>
@@ -20843,7 +20123,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" hidden="1" spans="1:13">
       <c r="A268" s="2" t="s">
         <v>1954</v>
       </c>
@@ -20884,7 +20164,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" hidden="1" spans="1:13">
       <c r="A269" s="2" t="s">
         <v>1954</v>
       </c>
@@ -20925,7 +20205,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" hidden="1" spans="1:13">
       <c r="A270" s="2" t="s">
         <v>1954</v>
       </c>
@@ -20966,7 +20246,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" hidden="1" spans="1:13">
       <c r="A271" s="2" t="s">
         <v>1954</v>
       </c>
@@ -21007,7 +20287,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" hidden="1" spans="1:13">
       <c r="A272" s="2" t="s">
         <v>1954</v>
       </c>
@@ -21048,7 +20328,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" hidden="1" spans="1:13">
       <c r="A273" s="2" t="s">
         <v>1954</v>
       </c>
@@ -21089,7 +20369,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" hidden="1" spans="1:13">
       <c r="A274" s="2" t="s">
         <v>1954</v>
       </c>
@@ -21130,7 +20410,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" hidden="1" spans="1:13">
       <c r="A275" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21171,7 +20451,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" hidden="1" spans="1:13">
       <c r="A276" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21212,7 +20492,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" hidden="1" spans="1:13">
       <c r="A277" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21253,7 +20533,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" hidden="1" spans="1:13">
       <c r="A278" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21294,7 +20574,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" hidden="1" spans="1:13">
       <c r="A279" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21335,7 +20615,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" hidden="1" spans="1:13">
       <c r="A280" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21376,7 +20656,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" hidden="1" spans="1:13">
       <c r="A281" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21417,7 +20697,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" hidden="1" spans="1:13">
       <c r="A282" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21458,7 +20738,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" hidden="1" spans="1:13">
       <c r="A283" s="2" t="s">
         <v>2030</v>
       </c>
@@ -21499,7 +20779,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" hidden="1" spans="1:13">
       <c r="A284" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21540,7 +20820,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" hidden="1" spans="1:13">
       <c r="A285" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21581,7 +20861,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" hidden="1" spans="1:13">
       <c r="A286" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21622,7 +20902,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" hidden="1" spans="1:13">
       <c r="A287" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21663,7 +20943,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" hidden="1" spans="1:13">
       <c r="A288" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21704,7 +20984,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" hidden="1" spans="1:13">
       <c r="A289" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21745,7 +21025,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" hidden="1" spans="1:13">
       <c r="A290" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21786,7 +21066,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" hidden="1" spans="1:13">
       <c r="A291" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21827,7 +21107,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" hidden="1" spans="1:13">
       <c r="A292" s="2" t="s">
         <v>2106</v>
       </c>
@@ -21868,7 +21148,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" hidden="1" spans="1:13">
       <c r="A293" s="2" t="s">
         <v>2183</v>
       </c>
@@ -21909,7 +21189,7 @@
         <v>2187</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" hidden="1" spans="1:13">
       <c r="A294" s="2" t="s">
         <v>2183</v>
       </c>
@@ -21950,7 +21230,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" hidden="1" spans="1:13">
       <c r="A295" s="2" t="s">
         <v>2183</v>
       </c>
@@ -21991,7 +21271,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" hidden="1" spans="1:13">
       <c r="A296" s="2" t="s">
         <v>2183</v>
       </c>
@@ -22030,7 +21310,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" hidden="1" spans="1:13">
       <c r="A297" s="2" t="s">
         <v>2183</v>
       </c>
@@ -22071,7 +21351,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" hidden="1" spans="1:13">
       <c r="A298" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22112,7 +21392,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" hidden="1" spans="1:13">
       <c r="A299" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22153,7 +21433,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" hidden="1" spans="1:13">
       <c r="A300" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22194,7 +21474,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" hidden="1" spans="1:13">
       <c r="A301" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22235,7 +21515,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" hidden="1" spans="1:13">
       <c r="A302" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22276,7 +21556,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" hidden="1" spans="1:13">
       <c r="A303" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22317,7 +21597,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" hidden="1" spans="1:13">
       <c r="A304" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22358,7 +21638,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" hidden="1" spans="1:13">
       <c r="A305" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22399,7 +21679,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" hidden="1" spans="1:13">
       <c r="A306" s="2" t="s">
         <v>2208</v>
       </c>
@@ -22440,7 +21720,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" hidden="1" spans="1:13">
       <c r="A307" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22481,7 +21761,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" hidden="1" spans="1:13">
       <c r="A308" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22522,7 +21802,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" hidden="1" spans="1:13">
       <c r="A309" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22563,7 +21843,7 @@
         <v>2311</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" hidden="1" spans="1:13">
       <c r="A310" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22604,7 +21884,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" hidden="1" spans="1:13">
       <c r="A311" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22645,7 +21925,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" hidden="1" spans="1:13">
       <c r="A312" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22686,7 +21966,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" hidden="1" spans="1:13">
       <c r="A313" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22727,7 +22007,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" hidden="1" spans="1:13">
       <c r="A314" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22768,7 +22048,7 @@
         <v>2354</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" hidden="1" spans="1:13">
       <c r="A315" s="2" t="s">
         <v>2285</v>
       </c>
@@ -22809,7 +22089,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" hidden="1" spans="1:13">
       <c r="A316" s="2" t="s">
         <v>2363</v>
       </c>
@@ -22850,7 +22130,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" hidden="1" spans="1:13">
       <c r="A317" s="2" t="s">
         <v>2363</v>
       </c>
@@ -22891,7 +22171,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" hidden="1" spans="1:13">
       <c r="A318" s="2" t="s">
         <v>2363</v>
       </c>
@@ -22932,7 +22212,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" hidden="1" spans="1:13">
       <c r="A319" s="2" t="s">
         <v>2363</v>
       </c>
@@ -22973,7 +22253,7 @@
         <v>2398</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" hidden="1" spans="1:13">
       <c r="A320" s="2" t="s">
         <v>2363</v>
       </c>
@@ -23014,7 +22294,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
+    <row r="321" hidden="1" spans="1:22">
       <c r="A321" s="2" t="s">
         <v>2363</v>
       </c>
@@ -23055,7 +22335,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
+    <row r="322" hidden="1" spans="1:22">
       <c r="A322" s="2" t="s">
         <v>2363</v>
       </c>
@@ -23096,7 +22376,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="323" spans="1:22">
+    <row r="323" hidden="1" spans="1:22">
       <c r="A323" s="2" t="s">
         <v>2363</v>
       </c>
@@ -23137,7 +22417,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="324" spans="1:22">
+    <row r="324" hidden="1" spans="1:22">
       <c r="A324" s="2" t="s">
         <v>2363</v>
       </c>
@@ -23178,7 +22458,7 @@
         <v>2439</v>
       </c>
     </row>
-    <row r="325" spans="1:22">
+    <row r="325" hidden="1" spans="1:22">
       <c r="A325" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23219,7 +22499,7 @@
         <v>41768</v>
       </c>
     </row>
-    <row r="326" spans="1:22">
+    <row r="326" hidden="1" spans="1:22">
       <c r="A326" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23260,7 +22540,7 @@
         <v>42732</v>
       </c>
     </row>
-    <row r="327" spans="1:22">
+    <row r="327" hidden="1" spans="1:22">
       <c r="A327" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23301,7 +22581,7 @@
         <v>19876</v>
       </c>
     </row>
-    <row r="328" spans="1:22">
+    <row r="328" hidden="1" spans="1:22">
       <c r="A328" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23342,7 +22622,7 @@
         <v>61599</v>
       </c>
     </row>
-    <row r="329" spans="1:22">
+    <row r="329" hidden="1" spans="1:22">
       <c r="A329" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23383,7 +22663,7 @@
         <v>90477</v>
       </c>
     </row>
-    <row r="330" spans="1:22">
+    <row r="330" hidden="1" spans="1:22">
       <c r="A330" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23424,7 +22704,7 @@
         <v>27466</v>
       </c>
     </row>
-    <row r="331" spans="1:22">
+    <row r="331" hidden="1" spans="1:22">
       <c r="A331" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23465,7 +22745,7 @@
         <v>141739</v>
       </c>
     </row>
-    <row r="332" spans="1:22">
+    <row r="332" hidden="1" spans="1:22">
       <c r="A332" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23510,7 +22790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:22">
+    <row r="333" hidden="1" spans="1:22">
       <c r="A333" s="2" t="s">
         <v>2440</v>
       </c>
@@ -23551,7 +22831,7 @@
         <v>53005</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
+    <row r="334" hidden="1" spans="1:22">
       <c r="A334" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23592,7 +22872,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="335" spans="1:22">
+    <row r="335" hidden="1" spans="1:22">
       <c r="A335" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23633,7 +22913,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="336" spans="1:22">
+    <row r="336" hidden="1" spans="1:22">
       <c r="A336" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23674,7 +22954,7 @@
         <v>2467</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" hidden="1" spans="1:13">
       <c r="A337" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23715,7 +22995,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" hidden="1" spans="1:13">
       <c r="A338" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23756,7 +23036,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" hidden="1" spans="1:13">
       <c r="A339" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23797,7 +23077,7 @@
         <v>2492</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" hidden="1" spans="1:13">
       <c r="A340" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23838,7 +23118,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" hidden="1" spans="1:13">
       <c r="A341" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23879,7 +23159,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" hidden="1" spans="1:13">
       <c r="A342" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23920,7 +23200,7 @@
         <v>2517</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" hidden="1" spans="1:13">
       <c r="A343" s="2" t="s">
         <v>2441</v>
       </c>
@@ -23957,7 +23237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" hidden="1" spans="1:13">
       <c r="A344" s="2" t="s">
         <v>2519</v>
       </c>
@@ -23998,7 +23278,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" hidden="1" spans="1:13">
       <c r="A345" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24039,7 +23319,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" hidden="1" spans="1:13">
       <c r="A346" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24080,7 +23360,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" hidden="1" spans="1:13">
       <c r="A347" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24121,7 +23401,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" hidden="1" spans="1:13">
       <c r="A348" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24162,7 +23442,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" hidden="1" spans="1:13">
       <c r="A349" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24203,7 +23483,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" hidden="1" spans="1:13">
       <c r="A350" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24244,7 +23524,7 @@
         <v>2578</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" hidden="1" spans="1:13">
       <c r="A351" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24285,7 +23565,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" hidden="1" spans="1:13">
       <c r="A352" s="2" t="s">
         <v>2519</v>
       </c>
@@ -24326,1813 +23606,2215 @@
         <v>2595</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
-      <c r="A353" s="5" t="s">
+    <row r="353" hidden="1" spans="1:13">
+      <c r="A353" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B353" s="5" t="s">
+      <c r="B353" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C353" s="5" t="s">
+      <c r="C353" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D353" s="5" t="s">
+      <c r="D353" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E353" s="5" t="s">
+      <c r="E353" s="2" t="s">
         <v>2190</v>
       </c>
-      <c r="F353" s="5" t="s">
+      <c r="F353" s="2" t="s">
         <v>1573</v>
       </c>
-      <c r="G353" s="5" t="s">
+      <c r="G353" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H353" s="5" t="s">
+      <c r="H353" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I353" s="5" t="s">
+      <c r="I353" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J353" s="5" t="s">
+      <c r="J353" s="2" t="s">
         <v>2597</v>
       </c>
-      <c r="K353" s="5" t="s">
+      <c r="K353" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="L353" s="5" t="s">
+      <c r="L353" s="2" t="s">
         <v>2598</v>
       </c>
-      <c r="M353" s="5" t="s">
+      <c r="M353" s="2" t="s">
         <v>2599</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
-      <c r="A354" s="5" t="s">
+    <row r="354" hidden="1" spans="1:13">
+      <c r="A354" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B354" s="5" t="s">
+      <c r="B354" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C354" s="5" t="s">
+      <c r="C354" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D354" s="5" t="s">
+      <c r="D354" s="2" t="s">
         <v>2600</v>
       </c>
-      <c r="E354" s="5" t="s">
+      <c r="E354" s="2" t="s">
         <v>2601</v>
       </c>
-      <c r="F354" s="5" t="s">
+      <c r="F354" s="2" t="s">
         <v>2602</v>
       </c>
-      <c r="G354" s="5" t="s">
+      <c r="G354" s="2" t="s">
         <v>2603</v>
       </c>
-      <c r="H354" s="5" t="s">
+      <c r="H354" s="2" t="s">
         <v>2604</v>
       </c>
-      <c r="I354" s="5" t="s">
+      <c r="I354" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="J354" s="5" t="s">
+      <c r="J354" s="2" t="s">
         <v>2605</v>
       </c>
-      <c r="K354" s="5" t="s">
+      <c r="K354" s="2" t="s">
         <v>2606</v>
       </c>
-      <c r="L354" s="5" t="s">
+      <c r="L354" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="M354" s="5" t="s">
+      <c r="M354" s="2" t="s">
         <v>2607</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
-      <c r="A355" s="5" t="s">
+    <row r="355" hidden="1" spans="1:13">
+      <c r="A355" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B355" s="5" t="s">
+      <c r="B355" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C355" s="5" t="s">
+      <c r="C355" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D355" s="5" t="s">
+      <c r="D355" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E355" s="5" t="s">
+      <c r="E355" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="F355" s="5" t="s">
+      <c r="F355" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G355" s="5" t="s">
+      <c r="G355" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H355" s="5" t="s">
+      <c r="H355" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="I355" s="5" t="s">
+      <c r="I355" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J355" s="5" t="s">
+      <c r="J355" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="K355" s="5" t="s">
+      <c r="K355" s="2" t="s">
         <v>2608</v>
       </c>
-      <c r="L355" s="5" t="s">
+      <c r="L355" s="2" t="s">
         <v>2609</v>
       </c>
-      <c r="M355" s="5" t="s">
+      <c r="M355" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
-      <c r="A356" s="5" t="s">
+    <row r="356" hidden="1" spans="1:13">
+      <c r="A356" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B356" s="5" t="s">
+      <c r="B356" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C356" s="5" t="s">
+      <c r="C356" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D356" s="5" t="s">
+      <c r="D356" s="2" t="s">
         <v>2610</v>
       </c>
-      <c r="E356" s="5" t="s">
+      <c r="E356" s="2" t="s">
         <v>2611</v>
       </c>
-      <c r="F356" s="5" t="s">
+      <c r="F356" s="2" t="s">
         <v>2612</v>
       </c>
-      <c r="G356" s="5" t="s">
+      <c r="G356" s="2" t="s">
         <v>2613</v>
       </c>
-      <c r="H356" s="5" t="s">
+      <c r="H356" s="2" t="s">
         <v>2614</v>
       </c>
-      <c r="I356" s="5" t="s">
+      <c r="I356" s="2" t="s">
         <v>2615</v>
       </c>
-      <c r="J356" s="5" t="s">
+      <c r="J356" s="2" t="s">
         <v>2616</v>
       </c>
-      <c r="K356" s="5" t="s">
+      <c r="K356" s="2" t="s">
         <v>2617</v>
       </c>
-      <c r="L356" s="5" t="s">
+      <c r="L356" s="2" t="s">
         <v>2618</v>
       </c>
-      <c r="M356" s="5" t="s">
+      <c r="M356" s="2" t="s">
         <v>2619</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
-      <c r="A357" s="5" t="s">
+    <row r="357" hidden="1" spans="1:13">
+      <c r="A357" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B357" s="5" t="s">
+      <c r="B357" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C357" s="5" t="s">
+      <c r="C357" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D357" s="5" t="s">
+      <c r="D357" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="E357" s="5" t="s">
+      <c r="E357" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="F357" s="5" t="s">
+      <c r="F357" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="G357" s="5" t="s">
+      <c r="G357" s="2" t="s">
         <v>2623</v>
       </c>
-      <c r="H357" s="5" t="s">
+      <c r="H357" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="I357" s="5" t="s">
+      <c r="I357" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="J357" s="5" t="s">
+      <c r="J357" s="2" t="s">
         <v>2626</v>
       </c>
-      <c r="K357" s="5" t="s">
+      <c r="K357" s="2" t="s">
         <v>2627</v>
       </c>
-      <c r="L357" s="5" t="s">
+      <c r="L357" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M357" s="5" t="s">
+      <c r="M357" s="2" t="s">
         <v>2628</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
-      <c r="A358" s="5" t="s">
+    <row r="358" hidden="1" spans="1:13">
+      <c r="A358" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B358" s="5" t="s">
+      <c r="B358" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C358" s="5" t="s">
+      <c r="C358" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D358" s="5" t="s">
+      <c r="D358" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E358" s="5" t="s">
+      <c r="E358" s="2" t="s">
         <v>953</v>
       </c>
-      <c r="F358" s="5" t="s">
+      <c r="F358" s="2" t="s">
         <v>2608</v>
       </c>
-      <c r="G358" s="5" t="s">
+      <c r="G358" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H358" s="5" t="s">
+      <c r="H358" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I358" s="5" t="s">
+      <c r="I358" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J358" s="5" t="s">
+      <c r="J358" s="2" t="s">
         <v>2629</v>
       </c>
-      <c r="K358" s="5" t="s">
+      <c r="K358" s="2" t="s">
         <v>2559</v>
       </c>
-      <c r="L358" s="5" t="s">
+      <c r="L358" s="2" t="s">
         <v>2630</v>
       </c>
-      <c r="M358" s="5" t="s">
+      <c r="M358" s="2" t="s">
         <v>2608</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
-      <c r="A359" s="5" t="s">
+    <row r="359" hidden="1" spans="1:13">
+      <c r="A359" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B359" s="5" t="s">
+      <c r="B359" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C359" s="5" t="s">
+      <c r="C359" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D359" s="5" t="s">
+      <c r="D359" s="2" t="s">
         <v>2631</v>
       </c>
-      <c r="E359" s="5" t="s">
+      <c r="E359" s="2" t="s">
         <v>2632</v>
       </c>
-      <c r="F359" s="5" t="s">
+      <c r="F359" s="2" t="s">
         <v>2633</v>
       </c>
-      <c r="G359" s="5" t="s">
+      <c r="G359" s="2" t="s">
         <v>2634</v>
       </c>
-      <c r="H359" s="5" t="s">
+      <c r="H359" s="2" t="s">
         <v>2635</v>
       </c>
-      <c r="I359" s="5" t="s">
+      <c r="I359" s="2" t="s">
         <v>2636</v>
       </c>
-      <c r="J359" s="5" t="s">
+      <c r="J359" s="2" t="s">
         <v>2637</v>
       </c>
-      <c r="K359" s="5" t="s">
+      <c r="K359" s="2" t="s">
         <v>2638</v>
       </c>
-      <c r="L359" s="5" t="s">
+      <c r="L359" s="2" t="s">
         <v>2639</v>
       </c>
-      <c r="M359" s="5" t="s">
+      <c r="M359" s="2" t="s">
         <v>2640</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
-      <c r="A360" s="5" t="s">
+    <row r="360" hidden="1" spans="1:13">
+      <c r="A360" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B360" s="5" t="s">
+      <c r="B360" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C360" s="5" t="s">
+      <c r="C360" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D360" s="5" t="s">
+      <c r="D360" s="2" t="s">
         <v>2641</v>
       </c>
-      <c r="E360" s="5" t="s">
+      <c r="E360" s="2" t="s">
         <v>2642</v>
       </c>
-      <c r="F360" s="5" t="s">
+      <c r="F360" s="2" t="s">
         <v>2643</v>
       </c>
-      <c r="G360" s="5" t="s">
+      <c r="G360" s="2" t="s">
         <v>2644</v>
       </c>
-      <c r="H360" s="5" t="s">
+      <c r="H360" s="2" t="s">
         <v>2645</v>
       </c>
-      <c r="I360" s="5" t="s">
+      <c r="I360" s="2" t="s">
         <v>2646</v>
       </c>
-      <c r="J360" s="5" t="s">
+      <c r="J360" s="2" t="s">
         <v>2647</v>
       </c>
-      <c r="K360" s="5" t="s">
+      <c r="K360" s="2" t="s">
         <v>2648</v>
       </c>
-      <c r="L360" s="5" t="s">
+      <c r="L360" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="M360" s="5" t="s">
+      <c r="M360" s="2" t="s">
         <v>2649</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
-      <c r="A361" s="5" t="s">
+    <row r="361" hidden="1" spans="1:13">
+      <c r="A361" s="2" t="s">
         <v>2596</v>
       </c>
-      <c r="B361" s="5" t="s">
+      <c r="B361" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C361" s="5" t="s">
+      <c r="C361" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D361" s="5" t="s">
+      <c r="D361" s="2" t="s">
         <v>2650</v>
       </c>
-      <c r="E361" s="5" t="s">
+      <c r="E361" s="2" t="s">
         <v>2651</v>
       </c>
-      <c r="F361" s="5" t="s">
+      <c r="F361" s="2" t="s">
         <v>2652</v>
       </c>
-      <c r="G361" s="5" t="s">
+      <c r="G361" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="H361" s="5" t="s">
+      <c r="H361" s="2" t="s">
         <v>2653</v>
       </c>
-      <c r="I361" s="5" t="s">
+      <c r="I361" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="J361" s="5" t="s">
+      <c r="J361" s="2" t="s">
         <v>2654</v>
       </c>
-      <c r="K361" s="5" t="s">
+      <c r="K361" s="2" t="s">
         <v>2655</v>
       </c>
-      <c r="L361" s="5" t="s">
+      <c r="L361" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="M361" s="5" t="s">
+      <c r="M361" s="2" t="s">
         <v>2656</v>
       </c>
     </row>
     <row r="362" spans="1:13">
-      <c r="A362" s="5" t="s">
+      <c r="A362" s="2" t="s">
         <v>2657</v>
       </c>
-      <c r="B362" s="5" t="s">
+      <c r="B362" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C362" s="5" t="s">
+      <c r="C362" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D362" s="5" t="s">
+      <c r="D362" s="3">
+        <v>0.00343871</v>
+      </c>
+      <c r="E362" s="3">
+        <v>302773</v>
+      </c>
+      <c r="F362" s="3">
+        <v>72120</v>
+      </c>
+      <c r="G362" s="3">
+        <v>20279</v>
+      </c>
+      <c r="H362" s="3">
+        <v>14107</v>
+      </c>
+      <c r="I362" s="3">
+        <v>248</v>
+      </c>
+      <c r="J362" s="3">
+        <v>1879967</v>
+      </c>
+      <c r="K362" s="3">
+        <v>940101</v>
+      </c>
+      <c r="L362" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="M362" s="3">
+        <v>84502</v>
+      </c>
+    </row>
+    <row r="363" hidden="1" spans="1:13">
+      <c r="A363" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B363" s="2" t="s">
         <v>2658</v>
       </c>
-      <c r="E362" s="5" t="s">
+      <c r="C363" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D363" s="3">
+        <v>0.00560159</v>
+      </c>
+      <c r="E363" s="3">
+        <v>84915</v>
+      </c>
+      <c r="F363" s="3">
+        <v>21601</v>
+      </c>
+      <c r="G363" s="3">
+        <v>6788</v>
+      </c>
+      <c r="H363" s="3">
+        <v>4271</v>
+      </c>
+      <c r="I363" s="3">
+        <v>121</v>
+      </c>
+      <c r="J363" s="3">
+        <v>481789</v>
+      </c>
+      <c r="K363" s="3">
+        <v>228486</v>
+      </c>
+      <c r="L363" s="3">
+        <v>0.56</v>
+      </c>
+      <c r="M363" s="3">
+        <v>24434</v>
+      </c>
+    </row>
+    <row r="364" hidden="1" spans="1:13">
+      <c r="A364" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D364" s="3">
+        <v>0.00122588</v>
+      </c>
+      <c r="E364" s="3">
+        <v>127821</v>
+      </c>
+      <c r="F364" s="3">
+        <v>34261</v>
+      </c>
+      <c r="G364" s="3">
+        <v>2523</v>
+      </c>
+      <c r="H364" s="3">
+        <v>2112</v>
+      </c>
+      <c r="I364" s="3">
+        <v>42</v>
+      </c>
+      <c r="J364" s="3">
+        <v>706552</v>
+      </c>
+      <c r="K364" s="3">
+        <v>125712</v>
+      </c>
+      <c r="L364" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="M364" s="3">
+        <v>36748</v>
+      </c>
+    </row>
+    <row r="365" hidden="1" spans="1:13">
+      <c r="A365" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D365" s="3">
+        <v>0.00068393</v>
+      </c>
+      <c r="E365" s="3">
+        <v>827316</v>
+      </c>
+      <c r="F365" s="3">
+        <v>214934</v>
+      </c>
+      <c r="G365" s="3">
+        <v>18087</v>
+      </c>
+      <c r="H365" s="3">
+        <v>15040</v>
+      </c>
+      <c r="I365" s="3">
+        <v>147</v>
+      </c>
+      <c r="J365" s="3">
+        <v>4533896</v>
+      </c>
+      <c r="K365" s="3">
+        <v>1061952</v>
+      </c>
+      <c r="L365" s="3">
+        <v>0.98</v>
+      </c>
+      <c r="M365" s="3">
+        <v>233544</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13">
+      <c r="A366" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D366" s="3">
+        <v>0.00631255</v>
+      </c>
+      <c r="E366" s="3">
+        <v>142242</v>
+      </c>
+      <c r="F366" s="3">
+        <v>25980</v>
+      </c>
+      <c r="G366" s="3">
+        <v>10201</v>
+      </c>
+      <c r="H366" s="3">
+        <v>6689</v>
+      </c>
+      <c r="I366" s="3">
+        <v>164</v>
+      </c>
+      <c r="J366" s="3">
+        <v>840225</v>
+      </c>
+      <c r="K366" s="3">
+        <v>546831</v>
+      </c>
+      <c r="L366" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="M366" s="3">
+        <v>33338</v>
+      </c>
+    </row>
+    <row r="367" hidden="1" spans="1:13">
+      <c r="A367" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D367" s="3">
+        <v>0.01972494</v>
+      </c>
+      <c r="E367" s="3">
+        <v>92913</v>
+      </c>
+      <c r="F367" s="3">
+        <v>34829</v>
+      </c>
+      <c r="G367" s="3">
+        <v>14822</v>
+      </c>
+      <c r="H367" s="3">
+        <v>9475</v>
+      </c>
+      <c r="I367" s="3">
+        <v>687</v>
+      </c>
+      <c r="J367" s="3">
+        <v>1083922</v>
+      </c>
+      <c r="K367" s="3">
+        <v>692548</v>
+      </c>
+      <c r="L367" s="3">
+        <v>0.78</v>
+      </c>
+      <c r="M367" s="3">
+        <v>43938</v>
+      </c>
+    </row>
+    <row r="368" spans="1:13">
+      <c r="A368" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D368" s="3">
+        <v>0.00957354</v>
+      </c>
+      <c r="E368" s="3">
+        <v>50139</v>
+      </c>
+      <c r="F368" s="3">
+        <v>8043</v>
+      </c>
+      <c r="G368" s="3">
+        <v>2608</v>
+      </c>
+      <c r="H368" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I368" s="3">
+        <v>77</v>
+      </c>
+      <c r="J368" s="3">
+        <v>333355</v>
+      </c>
+      <c r="K368" s="3">
+        <v>229435</v>
+      </c>
+      <c r="L368" s="3">
+        <v>1.47</v>
+      </c>
+      <c r="M368" s="3">
+        <v>11433</v>
+      </c>
+    </row>
+    <row r="369" hidden="1" spans="1:13">
+      <c r="A369" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D369" s="3">
+        <v>0.0018562</v>
+      </c>
+      <c r="E369" s="3">
+        <v>197669</v>
+      </c>
+      <c r="F369" s="3">
+        <v>58722</v>
+      </c>
+      <c r="G369" s="3">
+        <v>3329</v>
+      </c>
+      <c r="H369" s="3">
+        <v>2876</v>
+      </c>
+      <c r="I369" s="3">
+        <v>109</v>
+      </c>
+      <c r="J369" s="3">
+        <v>1137826</v>
+      </c>
+      <c r="K369" s="3">
+        <v>209398</v>
+      </c>
+      <c r="L369" s="3">
+        <v>1.05</v>
+      </c>
+      <c r="M369" s="3">
+        <v>62864</v>
+      </c>
+    </row>
+    <row r="370" hidden="1" spans="1:13">
+      <c r="A370" s="2" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D370" s="3">
+        <v>0.00097628</v>
+      </c>
+      <c r="E370" s="3">
+        <v>112031</v>
+      </c>
+      <c r="F370" s="3">
+        <v>24583</v>
+      </c>
+      <c r="G370" s="3">
+        <v>2464</v>
+      </c>
+      <c r="H370" s="3">
+        <v>1995</v>
+      </c>
+      <c r="I370" s="3">
+        <v>24</v>
+      </c>
+      <c r="J370" s="3">
+        <v>547891</v>
+      </c>
+      <c r="K370" s="3">
+        <v>159631</v>
+      </c>
+      <c r="L370" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="M370" s="3">
+        <v>27253</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13">
+      <c r="A371" s="2" t="s">
         <v>2659</v>
       </c>
-      <c r="F362" s="5" t="s">
+      <c r="B371" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D371" s="3">
+        <v>0.00237033</v>
+      </c>
+      <c r="E371" s="3">
+        <v>469498</v>
+      </c>
+      <c r="F371" s="3">
+        <v>121080</v>
+      </c>
+      <c r="G371" s="3">
+        <v>25118</v>
+      </c>
+      <c r="H371" s="3">
+        <v>17983</v>
+      </c>
+      <c r="I371" s="3">
+        <v>287</v>
+      </c>
+      <c r="J371" s="3">
+        <v>2914903</v>
+      </c>
+      <c r="K371" s="3">
+        <v>1224658</v>
+      </c>
+      <c r="L371" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="M371" s="3">
+        <v>138118</v>
+      </c>
+    </row>
+    <row r="372" hidden="1" spans="1:13">
+      <c r="A372" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D372" s="3">
+        <v>0.00087338</v>
+      </c>
+      <c r="E372" s="3">
+        <v>154217</v>
+      </c>
+      <c r="F372" s="3">
+        <v>51524</v>
+      </c>
+      <c r="G372" s="3">
+        <v>3307</v>
+      </c>
+      <c r="H372" s="3">
+        <v>2801</v>
+      </c>
+      <c r="I372" s="3">
+        <v>45</v>
+      </c>
+      <c r="J372" s="3">
+        <v>1024172</v>
+      </c>
+      <c r="K372" s="3">
+        <v>159160</v>
+      </c>
+      <c r="L372" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="M372" s="3">
+        <v>54967</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13">
+      <c r="A373" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D373" s="3">
+        <v>0.00563181</v>
+      </c>
+      <c r="E373" s="3">
+        <v>175903</v>
+      </c>
+      <c r="F373" s="3">
+        <v>35335</v>
+      </c>
+      <c r="G373" s="3">
+        <v>10831</v>
+      </c>
+      <c r="H373" s="3">
+        <v>7383</v>
+      </c>
+      <c r="I373" s="3">
+        <v>199</v>
+      </c>
+      <c r="J373" s="3">
+        <v>1039132</v>
+      </c>
+      <c r="K373" s="3">
+        <v>604271</v>
+      </c>
+      <c r="L373" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="M373" s="3">
+        <v>43659</v>
+      </c>
+    </row>
+    <row r="374" hidden="1" spans="1:13">
+      <c r="A374" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D374" s="3">
+        <v>0.00074776</v>
+      </c>
+      <c r="E374" s="3">
+        <v>743312</v>
+      </c>
+      <c r="F374" s="3">
+        <v>195249</v>
+      </c>
+      <c r="G374" s="3">
+        <v>19908</v>
+      </c>
+      <c r="H374" s="3">
+        <v>16480</v>
+      </c>
+      <c r="I374" s="3">
+        <v>146</v>
+      </c>
+      <c r="J374" s="3">
+        <v>4240465</v>
+      </c>
+      <c r="K374" s="3">
+        <v>1163770</v>
+      </c>
+      <c r="L374" s="3">
+        <v>0.97</v>
+      </c>
+      <c r="M374" s="3">
+        <v>214580</v>
+      </c>
+    </row>
+    <row r="375" hidden="1" spans="1:13">
+      <c r="A375" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D375" s="3">
+        <v>0.00483092</v>
+      </c>
+      <c r="E375" s="3">
+        <v>205145</v>
+      </c>
+      <c r="F375" s="3">
+        <v>57960</v>
+      </c>
+      <c r="G375" s="3">
+        <v>13626</v>
+      </c>
+      <c r="H375" s="3">
+        <v>9334</v>
+      </c>
+      <c r="I375" s="3">
+        <v>280</v>
+      </c>
+      <c r="J375" s="3">
+        <v>1254303</v>
+      </c>
+      <c r="K375" s="3">
+        <v>503013</v>
+      </c>
+      <c r="L375" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="M375" s="3">
+        <v>64439</v>
+      </c>
+    </row>
+    <row r="376" hidden="1" spans="1:13">
+      <c r="A376" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D376" s="3">
+        <v>0.00193933</v>
+      </c>
+      <c r="E376" s="3">
+        <v>192864</v>
+      </c>
+      <c r="F376" s="3">
+        <v>56205</v>
+      </c>
+      <c r="G376" s="3">
+        <v>2969</v>
+      </c>
+      <c r="H376" s="3">
+        <v>2582</v>
+      </c>
+      <c r="I376" s="3">
+        <v>109</v>
+      </c>
+      <c r="J376" s="3">
+        <v>1092150</v>
+      </c>
+      <c r="K376" s="3">
+        <v>183219</v>
+      </c>
+      <c r="L376" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="M376" s="3">
+        <v>59921</v>
+      </c>
+    </row>
+    <row r="377" hidden="1" spans="1:13">
+      <c r="A377" s="2" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D377" s="3">
+        <v>0.01818534</v>
+      </c>
+      <c r="E377" s="3">
+        <v>64457</v>
+      </c>
+      <c r="F377" s="3">
+        <v>20676</v>
+      </c>
+      <c r="G377" s="3">
+        <v>8093</v>
+      </c>
+      <c r="H377" s="3">
+        <v>5429</v>
+      </c>
+      <c r="I377" s="3">
+        <v>376</v>
+      </c>
+      <c r="J377" s="3">
+        <v>633974</v>
+      </c>
+      <c r="K377" s="3">
+        <v>395182</v>
+      </c>
+      <c r="L377" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="M377" s="3">
+        <v>25866</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13">
+      <c r="A378" s="5" t="s">
         <v>2660</v>
       </c>
-      <c r="G362" s="5" t="s">
+      <c r="B378" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D378" s="3">
+        <v>0.00309902</v>
+      </c>
+      <c r="E378" s="3">
+        <v>432305</v>
+      </c>
+      <c r="F378" s="3">
+        <v>105840</v>
+      </c>
+      <c r="G378" s="3">
+        <v>26735</v>
+      </c>
+      <c r="H378" s="3">
+        <v>18736</v>
+      </c>
+      <c r="I378" s="3">
+        <v>328</v>
+      </c>
+      <c r="J378" s="3">
+        <v>2666715</v>
+      </c>
+      <c r="K378" s="3">
+        <v>1265835</v>
+      </c>
+      <c r="L378" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="M378" s="3">
+        <v>122904</v>
+      </c>
+    </row>
+    <row r="379" hidden="1" spans="1:13">
+      <c r="A379" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D379" s="3">
+        <v>0.00092046</v>
+      </c>
+      <c r="E379" s="3">
+        <v>108689</v>
+      </c>
+      <c r="F379" s="3">
+        <v>26074</v>
+      </c>
+      <c r="G379" s="3">
+        <v>1618</v>
+      </c>
+      <c r="H379" s="3">
+        <v>1380</v>
+      </c>
+      <c r="I379" s="3">
+        <v>24</v>
+      </c>
+      <c r="J379" s="3">
+        <v>496055</v>
+      </c>
+      <c r="K379" s="3">
+        <v>87536</v>
+      </c>
+      <c r="L379" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="M379" s="3">
+        <v>27761</v>
+      </c>
+    </row>
+    <row r="380" hidden="1" spans="1:13">
+      <c r="A380" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B380" s="5" t="s">
         <v>2661</v>
       </c>
-      <c r="H362" s="5" t="s">
+      <c r="C380" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D380" s="3">
+        <v>0.0086426</v>
+      </c>
+      <c r="E380" s="3">
+        <v>3714</v>
+      </c>
+      <c r="F380" s="3">
+        <v>1967</v>
+      </c>
+      <c r="G380" s="3">
+        <v>1022</v>
+      </c>
+      <c r="H380" s="3">
+        <v>846</v>
+      </c>
+      <c r="I380" s="3">
+        <v>17</v>
+      </c>
+      <c r="J380" s="3">
+        <v>55014</v>
+      </c>
+      <c r="K380" s="3">
+        <v>34469</v>
+      </c>
+      <c r="L380" s="3">
+        <v>0.56</v>
+      </c>
+      <c r="M380" s="3">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="381" hidden="1" spans="1:13">
+      <c r="A381" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D381" s="3">
+        <v>0.00463665</v>
+      </c>
+      <c r="E381" s="3">
+        <v>293769</v>
+      </c>
+      <c r="F381" s="3">
+        <v>88426</v>
+      </c>
+      <c r="G381" s="3">
+        <v>18581</v>
+      </c>
+      <c r="H381" s="3">
+        <v>12423</v>
+      </c>
+      <c r="I381" s="3">
+        <v>410</v>
+      </c>
+      <c r="J381" s="3">
+        <v>1850595</v>
+      </c>
+      <c r="K381" s="3">
+        <v>726084</v>
+      </c>
+      <c r="L381" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="M381" s="3">
+        <v>98052</v>
+      </c>
+    </row>
+    <row r="382" hidden="1" spans="1:13">
+      <c r="A382" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D382" s="3">
+        <v>0.00099308</v>
+      </c>
+      <c r="E382" s="3">
+        <v>566542</v>
+      </c>
+      <c r="F382" s="3">
+        <v>139968</v>
+      </c>
+      <c r="G382" s="3">
+        <v>12312</v>
+      </c>
+      <c r="H382" s="3">
+        <v>10120</v>
+      </c>
+      <c r="I382" s="3">
+        <v>139</v>
+      </c>
+      <c r="J382" s="3">
+        <v>2981253</v>
+      </c>
+      <c r="K382" s="3">
+        <v>806093</v>
+      </c>
+      <c r="L382" s="3">
+        <v>1.09</v>
+      </c>
+      <c r="M382" s="3">
+        <v>153821</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13">
+      <c r="A383" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D383" s="3">
+        <v>0.00676869</v>
+      </c>
+      <c r="E383" s="3">
+        <v>133262</v>
+      </c>
+      <c r="F383" s="3">
+        <v>23786</v>
+      </c>
+      <c r="G383" s="3">
+        <v>8287</v>
+      </c>
+      <c r="H383" s="3">
+        <v>5686</v>
+      </c>
+      <c r="I383" s="3">
+        <v>161</v>
+      </c>
+      <c r="J383" s="3">
+        <v>786677</v>
+      </c>
+      <c r="K383" s="3">
+        <v>507587</v>
+      </c>
+      <c r="L383" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="M383" s="3">
+        <v>30838</v>
+      </c>
+    </row>
+    <row r="384" hidden="1" spans="1:13">
+      <c r="A384" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D384" s="3">
+        <v>0.04736842</v>
+      </c>
+      <c r="E384" s="3">
+        <v>1272</v>
+      </c>
+      <c r="F384" s="3">
+        <v>570</v>
+      </c>
+      <c r="G384" s="3">
+        <v>324</v>
+      </c>
+      <c r="H384" s="3">
+        <v>286</v>
+      </c>
+      <c r="I384" s="3">
+        <v>27</v>
+      </c>
+      <c r="J384" s="3">
+        <v>29181</v>
+      </c>
+      <c r="K384" s="3">
+        <v>22551</v>
+      </c>
+      <c r="L384" s="3">
+        <v>1.16</v>
+      </c>
+      <c r="M384" s="3">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="385" hidden="1" spans="1:13">
+      <c r="A385" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D385" s="3">
+        <v>0.00123097</v>
+      </c>
+      <c r="E385" s="3">
+        <v>214475</v>
+      </c>
+      <c r="F385" s="3">
+        <v>57678</v>
+      </c>
+      <c r="G385" s="3">
+        <v>3125</v>
+      </c>
+      <c r="H385" s="3">
+        <v>2734</v>
+      </c>
+      <c r="I385" s="3">
+        <v>71</v>
+      </c>
+      <c r="J385" s="3">
+        <v>1070946</v>
+      </c>
+      <c r="K385" s="3">
+        <v>177236</v>
+      </c>
+      <c r="L385" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="M385" s="3">
+        <v>61251</v>
+      </c>
+    </row>
+    <row r="386" hidden="1" spans="1:13">
+      <c r="A386" s="5" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D386" s="3">
+        <v>0.02093259</v>
+      </c>
+      <c r="E386" s="3">
+        <v>108174</v>
+      </c>
+      <c r="F386" s="3">
+        <v>32533</v>
+      </c>
+      <c r="G386" s="3">
+        <v>10981</v>
+      </c>
+      <c r="H386" s="3">
+        <v>7583</v>
+      </c>
+      <c r="I386" s="3">
+        <v>681</v>
+      </c>
+      <c r="J386" s="3">
+        <v>1079653</v>
+      </c>
+      <c r="K386" s="3">
+        <v>675233</v>
+      </c>
+      <c r="L386" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="M386" s="3">
+        <v>42056</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13">
+      <c r="A387" s="2" t="s">
         <v>2662</v>
       </c>
-      <c r="I362" s="5" t="s">
+      <c r="B387" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D387" s="3">
+        <v>0.00302144</v>
+      </c>
+      <c r="E387" s="3">
+        <v>306135</v>
+      </c>
+      <c r="F387" s="3">
+        <v>82411</v>
+      </c>
+      <c r="G387" s="3">
+        <v>21555</v>
+      </c>
+      <c r="H387" s="3">
+        <v>15020</v>
+      </c>
+      <c r="I387" s="3">
+        <v>249</v>
+      </c>
+      <c r="J387" s="3">
+        <v>2070161</v>
+      </c>
+      <c r="K387" s="3">
+        <v>977457</v>
+      </c>
+      <c r="L387" s="3">
+        <v>0.76</v>
+      </c>
+      <c r="M387" s="3">
+        <v>95302</v>
+      </c>
+    </row>
+    <row r="388" hidden="1" spans="1:13">
+      <c r="A388" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D388" s="3">
+        <v>0.00753819</v>
+      </c>
+      <c r="E388" s="3">
+        <v>9121</v>
+      </c>
+      <c r="F388" s="3">
+        <v>5041</v>
+      </c>
+      <c r="G388" s="3">
+        <v>2642</v>
+      </c>
+      <c r="H388" s="3">
+        <v>2266</v>
+      </c>
+      <c r="I388" s="3">
+        <v>38</v>
+      </c>
+      <c r="J388" s="3">
+        <v>139075</v>
+      </c>
+      <c r="K388" s="3">
+        <v>85111</v>
+      </c>
+      <c r="L388" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="M388" s="3">
+        <v>5920</v>
+      </c>
+    </row>
+    <row r="389" hidden="1" spans="1:13">
+      <c r="A389" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D389" s="3">
+        <v>0.00042283</v>
+      </c>
+      <c r="E389" s="3">
+        <v>10824</v>
+      </c>
+      <c r="F389" s="3">
+        <v>4730</v>
+      </c>
+      <c r="G389" s="3">
+        <v>306</v>
+      </c>
+      <c r="H389" s="3">
+        <v>245</v>
+      </c>
+      <c r="I389" s="3">
+        <v>2</v>
+      </c>
+      <c r="J389" s="3">
+        <v>90696</v>
+      </c>
+      <c r="K389" s="3">
+        <v>10985</v>
+      </c>
+      <c r="L389" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="M389" s="3">
+        <v>4955</v>
+      </c>
+    </row>
+    <row r="390" hidden="1" spans="1:13">
+      <c r="A390" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D390" s="3">
+        <v>0.00054963</v>
+      </c>
+      <c r="E390" s="3">
+        <v>395633</v>
+      </c>
+      <c r="F390" s="3">
+        <v>174662</v>
+      </c>
+      <c r="G390" s="3">
+        <v>16153</v>
+      </c>
+      <c r="H390" s="3">
+        <v>11942</v>
+      </c>
+      <c r="I390" s="3">
+        <v>96</v>
+      </c>
+      <c r="J390" s="3">
+        <v>3237856</v>
+      </c>
+      <c r="K390" s="3">
+        <v>747041</v>
+      </c>
+      <c r="L390" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="M390" s="3">
+        <v>186072</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13">
+      <c r="A391" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D391" s="3">
+        <v>0.00382119</v>
+      </c>
+      <c r="E391" s="3">
+        <v>175347</v>
+      </c>
+      <c r="F391" s="3">
+        <v>54695</v>
+      </c>
+      <c r="G391" s="3">
+        <v>13629</v>
+      </c>
+      <c r="H391" s="3">
+        <v>9563</v>
+      </c>
+      <c r="I391" s="3">
+        <v>209</v>
+      </c>
+      <c r="J391" s="3">
+        <v>1426802</v>
+      </c>
+      <c r="K391" s="3">
+        <v>724965</v>
+      </c>
+      <c r="L391" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="M391" s="3">
+        <v>64576</v>
+      </c>
+    </row>
+    <row r="392" hidden="1" spans="1:13">
+      <c r="A392" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D392" s="3">
+        <v>0.00403922</v>
+      </c>
+      <c r="E392" s="3">
+        <v>234498</v>
+      </c>
+      <c r="F392" s="3">
+        <v>71796</v>
+      </c>
+      <c r="G392" s="3">
+        <v>17069</v>
+      </c>
+      <c r="H392" s="3">
+        <v>11329</v>
+      </c>
+      <c r="I392" s="3">
+        <v>290</v>
+      </c>
+      <c r="J392" s="3">
+        <v>1606774</v>
+      </c>
+      <c r="K392" s="3">
+        <v>629885</v>
+      </c>
+      <c r="L392" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="M392" s="3">
+        <v>80231</v>
+      </c>
+    </row>
+    <row r="393" hidden="1" spans="1:13">
+      <c r="A393" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D393" s="3">
+        <v>0.04276316</v>
+      </c>
+      <c r="E393" s="3">
+        <v>1340</v>
+      </c>
+      <c r="F393" s="3">
+        <v>608</v>
+      </c>
+      <c r="G393" s="3">
+        <v>319</v>
+      </c>
+      <c r="H393" s="3">
+        <v>275</v>
+      </c>
+      <c r="I393" s="3">
+        <v>26</v>
+      </c>
+      <c r="J393" s="3">
+        <v>28620</v>
+      </c>
+      <c r="K393" s="3">
+        <v>21646</v>
+      </c>
+      <c r="L393" s="3">
+        <v>1.13</v>
+      </c>
+      <c r="M393" s="3">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="394" hidden="1" spans="1:13">
+      <c r="A394" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D394" s="3">
+        <v>0.0166484</v>
+      </c>
+      <c r="E394" s="3">
+        <v>149883</v>
+      </c>
+      <c r="F394" s="3">
+        <v>38322</v>
+      </c>
+      <c r="G394" s="3">
+        <v>12502</v>
+      </c>
+      <c r="H394" s="3">
+        <v>8459</v>
+      </c>
+      <c r="I394" s="3">
+        <v>638</v>
+      </c>
+      <c r="J394" s="3">
+        <v>1152561</v>
+      </c>
+      <c r="K394" s="3">
+        <v>676891</v>
+      </c>
+      <c r="L394" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="M394" s="3">
+        <v>47684</v>
+      </c>
+    </row>
+    <row r="395" hidden="1" spans="1:13">
+      <c r="A395" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D395" s="3">
+        <v>0.00151175</v>
+      </c>
+      <c r="E395" s="3">
+        <v>200339</v>
+      </c>
+      <c r="F395" s="3">
+        <v>65487</v>
+      </c>
+      <c r="G395" s="3">
+        <v>3961</v>
+      </c>
+      <c r="H395" s="3">
+        <v>3403</v>
+      </c>
+      <c r="I395" s="3">
+        <v>99</v>
+      </c>
+      <c r="J395" s="3">
+        <v>1273651</v>
+      </c>
+      <c r="K395" s="3">
+        <v>216996</v>
+      </c>
+      <c r="L395" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="M395" s="3">
+        <v>70089</v>
+      </c>
+    </row>
+    <row r="396" hidden="1" spans="1:13">
+      <c r="A396" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D396" s="3">
+        <v>0</v>
+      </c>
+      <c r="E396" s="3">
+        <v>2</v>
+      </c>
+      <c r="F396" s="3">
+        <v>1</v>
+      </c>
+      <c r="G396" s="3">
+        <v>1</v>
+      </c>
+      <c r="H396" s="3">
+        <v>0</v>
+      </c>
+      <c r="I396" s="3">
+        <v>0</v>
+      </c>
+      <c r="J396" s="3">
+        <v>8</v>
+      </c>
+      <c r="K396" s="3">
+        <v>2</v>
+      </c>
+      <c r="L396" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="M396" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" hidden="1" spans="1:13">
+      <c r="A397" s="2" t="s">
         <v>2663</v>
       </c>
-      <c r="J362" s="5" t="s">
+      <c r="B397" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D397" s="3">
+        <v>0.00589102</v>
+      </c>
+      <c r="E397" s="3">
+        <v>199257</v>
+      </c>
+      <c r="F397" s="3">
+        <v>66542</v>
+      </c>
+      <c r="G397" s="3">
+        <v>23043</v>
+      </c>
+      <c r="H397" s="3">
+        <v>14799</v>
+      </c>
+      <c r="I397" s="3">
+        <v>392</v>
+      </c>
+      <c r="J397" s="3">
+        <v>1638674</v>
+      </c>
+      <c r="K397" s="3">
+        <v>801883</v>
+      </c>
+      <c r="L397" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="M397" s="3">
+        <v>76467</v>
+      </c>
+    </row>
+    <row r="398" hidden="1" spans="1:13">
+      <c r="A398" s="2" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D398" s="3">
+        <v>0.00152369</v>
+      </c>
+      <c r="E398" s="3">
+        <v>346266</v>
+      </c>
+      <c r="F398" s="3">
+        <v>84663</v>
+      </c>
+      <c r="G398" s="3">
+        <v>14176</v>
+      </c>
+      <c r="H398" s="3">
+        <v>9870</v>
+      </c>
+      <c r="I398" s="3">
+        <v>129</v>
+      </c>
+      <c r="J398" s="3">
+        <v>1890111</v>
+      </c>
+      <c r="K398" s="3">
+        <v>715116</v>
+      </c>
+      <c r="L398" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="M398" s="3">
+        <v>94875</v>
+      </c>
+    </row>
+    <row r="399" hidden="1" spans="1:13">
+      <c r="A399" s="2" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D399" s="3">
+        <v>0.00623006</v>
+      </c>
+      <c r="E399" s="3">
+        <v>13467</v>
+      </c>
+      <c r="F399" s="3">
+        <v>6581</v>
+      </c>
+      <c r="G399" s="3">
+        <v>3188</v>
+      </c>
+      <c r="H399" s="3">
+        <v>2231</v>
+      </c>
+      <c r="I399" s="3">
+        <v>41</v>
+      </c>
+      <c r="J399" s="3">
+        <v>176905</v>
+      </c>
+      <c r="K399" s="3">
+        <v>100202</v>
+      </c>
+      <c r="L399" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="M399" s="3">
+        <v>7709</v>
+      </c>
+    </row>
+    <row r="400" hidden="1" spans="1:13">
+      <c r="A400" s="2" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D400" s="2" t="s">
         <v>2664</v>
       </c>
-      <c r="K362" s="5" t="s">
+      <c r="E400" s="2" t="s">
         <v>2665</v>
       </c>
-      <c r="L362" s="5" t="s">
-        <v>1559</v>
-      </c>
-      <c r="M362" s="5" t="s">
+      <c r="F400" s="2" t="s">
         <v>2666</v>
       </c>
-    </row>
-    <row r="363" spans="1:13">
-      <c r="A363" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B363" s="5" t="s">
+      <c r="G400" s="2" t="s">
         <v>2667</v>
       </c>
-      <c r="C363" s="5" t="s">
+      <c r="H400" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>2669</v>
+      </c>
+      <c r="J400" s="2" t="s">
+        <v>2670</v>
+      </c>
+      <c r="K400" s="2" t="s">
+        <v>2671</v>
+      </c>
+      <c r="L400" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="M400" s="2" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="401" hidden="1" spans="1:14">
+      <c r="A401" s="2" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>2673</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F401" s="2" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G401" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H401" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I401" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="J401" s="2" t="s">
+        <v>2676</v>
+      </c>
+      <c r="K401" s="2" t="s">
+        <v>2677</v>
+      </c>
+      <c r="L401" s="2" t="s">
+        <v>2639</v>
+      </c>
+      <c r="M401" s="2" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="402" hidden="1" spans="1:14">
+      <c r="A402" s="6" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B402" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C402" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D363" s="5" t="s">
-        <v>2668</v>
-      </c>
-      <c r="E363" s="5" t="s">
-        <v>2669</v>
-      </c>
-      <c r="F363" s="5" t="s">
-        <v>2670</v>
-      </c>
-      <c r="G363" s="5" t="s">
-        <v>2671</v>
-      </c>
-      <c r="H363" s="5" t="s">
-        <v>1556</v>
-      </c>
-      <c r="I363" s="5" t="s">
-        <v>2672</v>
-      </c>
-      <c r="J363" s="5" t="s">
-        <v>2673</v>
-      </c>
-      <c r="K363" s="5" t="s">
-        <v>2674</v>
-      </c>
-      <c r="L363" s="5" t="s">
+      <c r="D402" s="6" t="s">
+        <v>2680</v>
+      </c>
+      <c r="E402" s="6" t="s">
+        <v>2681</v>
+      </c>
+      <c r="F402" s="6" t="s">
+        <v>2682</v>
+      </c>
+      <c r="G402" s="6" t="s">
+        <v>2683</v>
+      </c>
+      <c r="H402" s="6" t="s">
+        <v>2684</v>
+      </c>
+      <c r="I402" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J402" s="6" t="s">
+        <v>2685</v>
+      </c>
+      <c r="K402" s="6" t="s">
+        <v>2686</v>
+      </c>
+      <c r="L402" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M402" s="6" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="403" hidden="1" spans="1:14">
+      <c r="A403" s="6" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B403" s="6" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C403" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D403" s="6" t="s">
+        <v>2688</v>
+      </c>
+      <c r="E403" s="6" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F403" s="6" t="s">
+        <v>2690</v>
+      </c>
+      <c r="G403" s="6" t="s">
+        <v>2691</v>
+      </c>
+      <c r="H403" s="6" t="s">
+        <v>2692</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="J403" s="6" t="s">
+        <v>2693</v>
+      </c>
+      <c r="K403" s="6" t="s">
+        <v>2694</v>
+      </c>
+      <c r="L403" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="M363" s="5" t="s">
-        <v>2675</v>
-      </c>
-    </row>
-    <row r="364" spans="1:13">
-      <c r="A364" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B364" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C364" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D364" s="5" t="s">
-        <v>2676</v>
-      </c>
-      <c r="E364" s="5" t="s">
-        <v>2677</v>
-      </c>
-      <c r="F364" s="5" t="s">
-        <v>2678</v>
-      </c>
-      <c r="G364" s="5" t="s">
+      <c r="M403" s="6" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="404" hidden="1" spans="1:14">
+      <c r="A404" s="6" t="s">
         <v>2679</v>
       </c>
-      <c r="H364" s="5" t="s">
-        <v>2680</v>
-      </c>
-      <c r="I364" s="5" t="s">
-        <v>2681</v>
-      </c>
-      <c r="J364" s="5" t="s">
-        <v>2682</v>
-      </c>
-      <c r="K364" s="5" t="s">
-        <v>2683</v>
-      </c>
-      <c r="L364" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="M364" s="5" t="s">
-        <v>2684</v>
-      </c>
-    </row>
-    <row r="365" spans="1:13">
-      <c r="A365" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B365" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C365" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D365" s="5" t="s">
-        <v>2685</v>
-      </c>
-      <c r="E365" s="5" t="s">
-        <v>2686</v>
-      </c>
-      <c r="F365" s="5" t="s">
-        <v>2687</v>
-      </c>
-      <c r="G365" s="5" t="s">
-        <v>2688</v>
-      </c>
-      <c r="H365" s="5" t="s">
-        <v>2689</v>
-      </c>
-      <c r="I365" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="J365" s="5" t="s">
-        <v>2690</v>
-      </c>
-      <c r="K365" s="5" t="s">
-        <v>2691</v>
-      </c>
-      <c r="L365" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="M365" s="5" t="s">
-        <v>2692</v>
-      </c>
-    </row>
-    <row r="366" spans="1:13">
-      <c r="A366" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B366" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C366" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D366" s="5" t="s">
-        <v>2693</v>
-      </c>
-      <c r="E366" s="5" t="s">
-        <v>2694</v>
-      </c>
-      <c r="F366" s="5" t="s">
-        <v>2695</v>
-      </c>
-      <c r="G366" s="5" t="s">
+      <c r="B404" s="6" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C404" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D404" s="6" t="s">
         <v>2696</v>
       </c>
-      <c r="H366" s="5" t="s">
+      <c r="E404" s="6" t="s">
         <v>2697</v>
       </c>
-      <c r="I366" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="J366" s="5" t="s">
+      <c r="F404" s="6" t="s">
         <v>2698</v>
       </c>
-      <c r="K366" s="5" t="s">
+      <c r="G404" s="6" t="s">
         <v>2699</v>
       </c>
-      <c r="L366" s="5" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M366" s="5" t="s">
+      <c r="H404" s="6" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I404" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J404" s="6" t="s">
         <v>2700</v>
       </c>
-    </row>
-    <row r="367" spans="1:13">
-      <c r="A367" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B367" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C367" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D367" s="5" t="s">
+      <c r="K404" s="6" t="s">
         <v>2701</v>
       </c>
-      <c r="E367" s="5" t="s">
+      <c r="L404" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="M404" s="6" t="s">
         <v>2702</v>
       </c>
-      <c r="F367" s="5" t="s">
-        <v>2703</v>
-      </c>
-      <c r="G367" s="5" t="s">
-        <v>2704</v>
-      </c>
-      <c r="H367" s="5" t="s">
-        <v>2705</v>
-      </c>
-      <c r="I367" s="5" t="s">
-        <v>2706</v>
-      </c>
-      <c r="J367" s="5" t="s">
-        <v>2707</v>
-      </c>
-      <c r="K367" s="5" t="s">
-        <v>2708</v>
-      </c>
-      <c r="L367" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="M367" s="5" t="s">
-        <v>2709</v>
-      </c>
-    </row>
-    <row r="368" spans="1:13">
-      <c r="A368" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B368" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C368" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D368" s="5" t="s">
-        <v>2710</v>
-      </c>
-      <c r="E368" s="5" t="s">
-        <v>2711</v>
-      </c>
-      <c r="F368" s="5" t="s">
-        <v>2712</v>
-      </c>
-      <c r="G368" s="5" t="s">
-        <v>2713</v>
-      </c>
-      <c r="H368" s="5" t="s">
-        <v>2714</v>
-      </c>
-      <c r="I368" s="5" t="s">
-        <v>1182</v>
-      </c>
-      <c r="J368" s="5" t="s">
-        <v>2715</v>
-      </c>
-      <c r="K368" s="5" t="s">
-        <v>2716</v>
-      </c>
-      <c r="L368" s="5" t="s">
-        <v>2717</v>
-      </c>
-      <c r="M368" s="5" t="s">
-        <v>2718</v>
-      </c>
-    </row>
-    <row r="369" spans="1:13">
-      <c r="A369" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B369" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C369" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D369" s="5" t="s">
-        <v>2719</v>
-      </c>
-      <c r="E369" s="5" t="s">
-        <v>2720</v>
-      </c>
-      <c r="F369" s="5" t="s">
-        <v>2721</v>
-      </c>
-      <c r="G369" s="5" t="s">
-        <v>2722</v>
-      </c>
-      <c r="H369" s="5" t="s">
-        <v>2723</v>
-      </c>
-      <c r="I369" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J369" s="5" t="s">
-        <v>2724</v>
-      </c>
-      <c r="K369" s="5" t="s">
-        <v>2725</v>
-      </c>
-      <c r="L369" s="5" t="s">
-        <v>1287</v>
-      </c>
-      <c r="M369" s="5" t="s">
-        <v>2726</v>
-      </c>
-    </row>
-    <row r="370" spans="1:13">
-      <c r="A370" s="5" t="s">
-        <v>2657</v>
-      </c>
-      <c r="B370" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C370" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D370" s="5" t="s">
-        <v>2727</v>
-      </c>
-      <c r="E370" s="5" t="s">
-        <v>2728</v>
-      </c>
-      <c r="F370" s="5" t="s">
-        <v>2729</v>
-      </c>
-      <c r="G370" s="5" t="s">
-        <v>2730</v>
-      </c>
-      <c r="H370" s="5" t="s">
-        <v>2731</v>
-      </c>
-      <c r="I370" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J370" s="5" t="s">
-        <v>2732</v>
-      </c>
-      <c r="K370" s="5" t="s">
-        <v>2733</v>
-      </c>
-      <c r="L370" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="M370" s="5" t="s">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="371" spans="1:13">
-      <c r="A371" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B371" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D371" s="5" t="s">
-        <v>2736</v>
-      </c>
-      <c r="E371" s="5" t="s">
-        <v>2737</v>
-      </c>
-      <c r="F371" s="5" t="s">
-        <v>2738</v>
-      </c>
-      <c r="G371" s="5" t="s">
-        <v>2739</v>
-      </c>
-      <c r="H371" s="5" t="s">
-        <v>2740</v>
-      </c>
-      <c r="I371" s="5" t="s">
-        <v>1889</v>
-      </c>
-      <c r="J371" s="5" t="s">
-        <v>2741</v>
-      </c>
-      <c r="K371" s="5" t="s">
-        <v>2742</v>
-      </c>
-      <c r="L371" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M371" s="5" t="s">
-        <v>2743</v>
-      </c>
-    </row>
-    <row r="372" spans="1:13">
-      <c r="A372" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B372" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C372" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D372" s="5" t="s">
-        <v>2744</v>
-      </c>
-      <c r="E372" s="5" t="s">
-        <v>2745</v>
-      </c>
-      <c r="F372" s="5" t="s">
-        <v>2746</v>
-      </c>
-      <c r="G372" s="5" t="s">
-        <v>2747</v>
-      </c>
-      <c r="H372" s="5" t="s">
-        <v>2748</v>
-      </c>
-      <c r="I372" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="J372" s="5" t="s">
-        <v>2749</v>
-      </c>
-      <c r="K372" s="5" t="s">
-        <v>2750</v>
-      </c>
-      <c r="L372" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="M372" s="5" t="s">
-        <v>2751</v>
-      </c>
-    </row>
-    <row r="373" spans="1:13">
-      <c r="A373" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B373" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D373" s="5" t="s">
-        <v>2752</v>
-      </c>
-      <c r="E373" s="5" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F373" s="5" t="s">
-        <v>2754</v>
-      </c>
-      <c r="G373" s="5" t="s">
-        <v>2755</v>
-      </c>
-      <c r="H373" s="5" t="s">
-        <v>2756</v>
-      </c>
-      <c r="I373" s="5" t="s">
-        <v>979</v>
-      </c>
-      <c r="J373" s="5" t="s">
-        <v>2757</v>
-      </c>
-      <c r="K373" s="5" t="s">
-        <v>2758</v>
-      </c>
-      <c r="L373" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="M373" s="5" t="s">
-        <v>2759</v>
-      </c>
-    </row>
-    <row r="374" spans="1:13">
-      <c r="A374" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B374" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D374" s="5" t="s">
-        <v>2760</v>
-      </c>
-      <c r="E374" s="5" t="s">
-        <v>2761</v>
-      </c>
-      <c r="F374" s="5" t="s">
-        <v>2762</v>
-      </c>
-      <c r="G374" s="5" t="s">
-        <v>2763</v>
-      </c>
-      <c r="H374" s="5" t="s">
-        <v>2764</v>
-      </c>
-      <c r="I374" s="5" t="s">
-        <v>2765</v>
-      </c>
-      <c r="J374" s="5" t="s">
-        <v>2766</v>
-      </c>
-      <c r="K374" s="5" t="s">
-        <v>2767</v>
-      </c>
-      <c r="L374" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="M374" s="5" t="s">
-        <v>2768</v>
-      </c>
-    </row>
-    <row r="375" spans="1:13">
-      <c r="A375" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B375" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D375" s="5" t="s">
-        <v>2769</v>
-      </c>
-      <c r="E375" s="5" t="s">
-        <v>2770</v>
-      </c>
-      <c r="F375" s="5" t="s">
-        <v>2771</v>
-      </c>
-      <c r="G375" s="5" t="s">
-        <v>2772</v>
-      </c>
-      <c r="H375" s="5" t="s">
-        <v>2773</v>
-      </c>
-      <c r="I375" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="J375" s="5" t="s">
-        <v>2774</v>
-      </c>
-      <c r="K375" s="5" t="s">
-        <v>2775</v>
-      </c>
-      <c r="L375" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="M375" s="5" t="s">
-        <v>2776</v>
-      </c>
-    </row>
-    <row r="376" spans="1:13">
-      <c r="A376" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B376" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C376" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D376" s="5" t="s">
-        <v>2777</v>
-      </c>
-      <c r="E376" s="5" t="s">
-        <v>2778</v>
-      </c>
-      <c r="F376" s="5" t="s">
-        <v>2779</v>
-      </c>
-      <c r="G376" s="5" t="s">
-        <v>2780</v>
-      </c>
-      <c r="H376" s="5" t="s">
-        <v>2781</v>
-      </c>
-      <c r="I376" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J376" s="5" t="s">
-        <v>2782</v>
-      </c>
-      <c r="K376" s="5" t="s">
-        <v>2783</v>
-      </c>
-      <c r="L376" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="M376" s="5" t="s">
-        <v>2784</v>
-      </c>
-    </row>
-    <row r="377" spans="1:13">
-      <c r="A377" s="5" t="s">
-        <v>2735</v>
-      </c>
-      <c r="B377" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C377" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D377" s="5" t="s">
-        <v>2785</v>
-      </c>
-      <c r="E377" s="5" t="s">
-        <v>2786</v>
-      </c>
-      <c r="F377" s="5" t="s">
-        <v>2787</v>
-      </c>
-      <c r="G377" s="5" t="s">
-        <v>2788</v>
-      </c>
-      <c r="H377" s="5" t="s">
-        <v>2789</v>
-      </c>
-      <c r="I377" s="5" t="s">
-        <v>2271</v>
-      </c>
-      <c r="J377" s="5" t="s">
-        <v>2790</v>
-      </c>
-      <c r="K377" s="5" t="s">
-        <v>2791</v>
-      </c>
-      <c r="L377" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="M377" s="5" t="s">
-        <v>2792</v>
-      </c>
-    </row>
-    <row r="378" spans="1:13">
-      <c r="A378" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B378" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D378" s="5" t="s">
-        <v>2794</v>
-      </c>
-      <c r="E378" s="5" t="s">
-        <v>2795</v>
-      </c>
-      <c r="F378" s="5" t="s">
-        <v>2796</v>
-      </c>
-      <c r="G378" s="5" t="s">
-        <v>2797</v>
-      </c>
-      <c r="H378" s="5" t="s">
-        <v>2798</v>
-      </c>
-      <c r="I378" s="5" t="s">
-        <v>2799</v>
-      </c>
-      <c r="J378" s="5" t="s">
-        <v>2800</v>
-      </c>
-      <c r="K378" s="5" t="s">
-        <v>2801</v>
-      </c>
-      <c r="L378" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="M378" s="5" t="s">
-        <v>2802</v>
-      </c>
-    </row>
-    <row r="379" spans="1:13">
-      <c r="A379" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B379" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C379" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D379" s="5" t="s">
-        <v>2803</v>
-      </c>
-      <c r="E379" s="5" t="s">
-        <v>2804</v>
-      </c>
-      <c r="F379" s="5" t="s">
-        <v>2805</v>
-      </c>
-      <c r="G379" s="5" t="s">
-        <v>2806</v>
-      </c>
-      <c r="H379" s="5" t="s">
-        <v>2807</v>
-      </c>
-      <c r="I379" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J379" s="5" t="s">
-        <v>2808</v>
-      </c>
-      <c r="K379" s="5" t="s">
-        <v>2809</v>
-      </c>
-      <c r="L379" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="M379" s="5" t="s">
-        <v>2810</v>
-      </c>
-    </row>
-    <row r="380" spans="1:13">
-      <c r="A380" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B380" s="6" t="s">
-        <v>2811</v>
-      </c>
-      <c r="C380" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D380" s="5" t="s">
-        <v>2812</v>
-      </c>
-      <c r="E380" s="5" t="s">
-        <v>2813</v>
-      </c>
-      <c r="F380" s="5" t="s">
-        <v>2814</v>
-      </c>
-      <c r="G380" s="5" t="s">
-        <v>2815</v>
-      </c>
-      <c r="H380" s="5" t="s">
-        <v>2816</v>
-      </c>
-      <c r="I380" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="J380" s="5" t="s">
-        <v>2817</v>
-      </c>
-      <c r="K380" s="5" t="s">
-        <v>2818</v>
-      </c>
-      <c r="L380" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="M380" s="5" t="s">
-        <v>2819</v>
-      </c>
-    </row>
-    <row r="381" spans="1:13">
-      <c r="A381" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B381" s="6" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C381" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D381" s="5" t="s">
-        <v>2820</v>
-      </c>
-      <c r="E381" s="5" t="s">
-        <v>2821</v>
-      </c>
-      <c r="F381" s="5" t="s">
-        <v>2822</v>
-      </c>
-      <c r="G381" s="5" t="s">
-        <v>2823</v>
-      </c>
-      <c r="H381" s="5" t="s">
-        <v>2824</v>
-      </c>
-      <c r="I381" s="5" t="s">
-        <v>2825</v>
-      </c>
-      <c r="J381" s="5" t="s">
-        <v>2826</v>
-      </c>
-      <c r="K381" s="5" t="s">
-        <v>2827</v>
-      </c>
-      <c r="L381" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="M381" s="5" t="s">
-        <v>2828</v>
-      </c>
-    </row>
-    <row r="382" spans="1:13">
-      <c r="A382" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B382" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C382" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D382" s="5" t="s">
-        <v>2829</v>
-      </c>
-      <c r="E382" s="5" t="s">
-        <v>2830</v>
-      </c>
-      <c r="F382" s="5" t="s">
-        <v>2831</v>
-      </c>
-      <c r="G382" s="5" t="s">
-        <v>2832</v>
-      </c>
-      <c r="H382" s="5" t="s">
-        <v>2833</v>
-      </c>
-      <c r="I382" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="J382" s="5" t="s">
-        <v>2834</v>
-      </c>
-      <c r="K382" s="5" t="s">
-        <v>2835</v>
-      </c>
-      <c r="L382" s="5" t="s">
-        <v>1683</v>
-      </c>
-      <c r="M382" s="5" t="s">
-        <v>2836</v>
-      </c>
-    </row>
-    <row r="383" spans="1:13">
-      <c r="A383" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B383" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C383" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D383" s="5" t="s">
-        <v>2837</v>
-      </c>
-      <c r="E383" s="5" t="s">
-        <v>2838</v>
-      </c>
-      <c r="F383" s="5" t="s">
-        <v>2839</v>
-      </c>
-      <c r="G383" s="5" t="s">
-        <v>2840</v>
-      </c>
-      <c r="H383" s="5" t="s">
-        <v>2841</v>
-      </c>
-      <c r="I383" s="5" t="s">
-        <v>1407</v>
-      </c>
-      <c r="J383" s="5" t="s">
-        <v>2842</v>
-      </c>
-      <c r="K383" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="L383" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="M383" s="5" t="s">
-        <v>2844</v>
-      </c>
-    </row>
-    <row r="384" spans="1:13">
-      <c r="A384" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B384" s="6" t="s">
-        <v>2811</v>
-      </c>
-      <c r="C384" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D384" s="5" t="s">
-        <v>2845</v>
-      </c>
-      <c r="E384" s="5" t="s">
-        <v>2846</v>
-      </c>
-      <c r="F384" s="5" t="s">
-        <v>2847</v>
-      </c>
-      <c r="G384" s="5" t="s">
-        <v>2848</v>
-      </c>
-      <c r="H384" s="5" t="s">
-        <v>1398</v>
-      </c>
-      <c r="I384" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="J384" s="5" t="s">
-        <v>2849</v>
-      </c>
-      <c r="K384" s="5" t="s">
-        <v>2850</v>
-      </c>
-      <c r="L384" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="M384" s="5" t="s">
-        <v>2851</v>
-      </c>
-    </row>
-    <row r="385" spans="1:13">
-      <c r="A385" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B385" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C385" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D385" s="5" t="s">
-        <v>2852</v>
-      </c>
-      <c r="E385" s="5" t="s">
-        <v>2853</v>
-      </c>
-      <c r="F385" s="5" t="s">
-        <v>2854</v>
-      </c>
-      <c r="G385" s="5" t="s">
-        <v>2855</v>
-      </c>
-      <c r="H385" s="5" t="s">
-        <v>2856</v>
-      </c>
-      <c r="I385" s="5" t="s">
-        <v>953</v>
-      </c>
-      <c r="J385" s="5" t="s">
-        <v>2857</v>
-      </c>
-      <c r="K385" s="5" t="s">
-        <v>2858</v>
-      </c>
-      <c r="L385" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="M385" s="5" t="s">
-        <v>2859</v>
-      </c>
-    </row>
-    <row r="386" spans="1:13">
-      <c r="A386" s="6" t="s">
-        <v>2793</v>
-      </c>
-      <c r="B386" s="6" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C386" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D386" s="5" t="s">
-        <v>2860</v>
-      </c>
-      <c r="E386" s="5" t="s">
-        <v>2861</v>
-      </c>
-      <c r="F386" s="5" t="s">
-        <v>2862</v>
-      </c>
-      <c r="G386" s="5" t="s">
-        <v>2863</v>
-      </c>
-      <c r="H386" s="5" t="s">
-        <v>2864</v>
-      </c>
-      <c r="I386" s="5" t="s">
-        <v>2865</v>
-      </c>
-      <c r="J386" s="5" t="s">
-        <v>2866</v>
-      </c>
-      <c r="K386" s="5" t="s">
-        <v>2867</v>
-      </c>
-      <c r="L386" s="5" t="s">
-        <v>402</v>
-      </c>
-      <c r="M386" s="5" t="s">
-        <v>2868</v>
-      </c>
-    </row>
-    <row r="387" spans="1:13">
-      <c r="A387" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B387" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C387" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D387" s="5" t="s">
-        <v>2870</v>
-      </c>
-      <c r="E387" s="5" t="s">
-        <v>2871</v>
-      </c>
-      <c r="F387" s="5" t="s">
-        <v>2872</v>
-      </c>
-      <c r="G387" s="5" t="s">
-        <v>2873</v>
-      </c>
-      <c r="H387" s="5" t="s">
-        <v>2874</v>
-      </c>
-      <c r="I387" s="5" t="s">
-        <v>1700</v>
-      </c>
-      <c r="J387" s="5" t="s">
-        <v>2875</v>
-      </c>
-      <c r="K387" s="5" t="s">
-        <v>2876</v>
-      </c>
-      <c r="L387" s="5" t="s">
-        <v>751</v>
-      </c>
-      <c r="M387" s="5" t="s">
-        <v>2877</v>
-      </c>
-    </row>
-    <row r="388" spans="1:13">
-      <c r="A388" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B388" s="5" t="s">
-        <v>2811</v>
-      </c>
-      <c r="C388" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D388" s="5" t="s">
-        <v>2878</v>
-      </c>
-      <c r="E388" s="5" t="s">
-        <v>2879</v>
-      </c>
-      <c r="F388" s="5" t="s">
-        <v>2880</v>
-      </c>
-      <c r="G388" s="5" t="s">
-        <v>2881</v>
-      </c>
-      <c r="H388" s="5" t="s">
-        <v>2882</v>
-      </c>
-      <c r="I388" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="J388" s="5" t="s">
-        <v>2883</v>
-      </c>
-      <c r="K388" s="5" t="s">
-        <v>2884</v>
-      </c>
-      <c r="L388" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="M388" s="5" t="s">
-        <v>2885</v>
-      </c>
-    </row>
-    <row r="389" spans="1:13">
-      <c r="A389" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B389" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C389" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D389" s="5" t="s">
-        <v>2886</v>
-      </c>
-      <c r="E389" s="5" t="s">
-        <v>2887</v>
-      </c>
-      <c r="F389" s="5" t="s">
-        <v>2888</v>
-      </c>
-      <c r="G389" s="5" t="s">
-        <v>2889</v>
-      </c>
-      <c r="H389" s="5" t="s">
-        <v>1702</v>
-      </c>
-      <c r="I389" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J389" s="5" t="s">
-        <v>2890</v>
-      </c>
-      <c r="K389" s="5" t="s">
-        <v>2891</v>
-      </c>
-      <c r="L389" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="M389" s="5" t="s">
-        <v>2892</v>
-      </c>
-    </row>
-    <row r="390" spans="1:13">
-      <c r="A390" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B390" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C390" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D390" s="5" t="s">
-        <v>2893</v>
-      </c>
-      <c r="E390" s="5" t="s">
-        <v>2894</v>
-      </c>
-      <c r="F390" s="5" t="s">
-        <v>2895</v>
-      </c>
-      <c r="G390" s="5" t="s">
-        <v>2896</v>
-      </c>
-      <c r="H390" s="5" t="s">
-        <v>2897</v>
-      </c>
-      <c r="I390" s="5" t="s">
-        <v>2898</v>
-      </c>
-      <c r="J390" s="5" t="s">
-        <v>2899</v>
-      </c>
-      <c r="K390" s="5" t="s">
-        <v>2900</v>
-      </c>
-      <c r="L390" s="5" t="s">
-        <v>1559</v>
-      </c>
-      <c r="M390" s="5" t="s">
-        <v>2901</v>
-      </c>
-    </row>
-    <row r="391" spans="1:13">
-      <c r="A391" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B391" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C391" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D391" s="5" t="s">
-        <v>2902</v>
-      </c>
-      <c r="E391" s="5" t="s">
-        <v>2903</v>
-      </c>
-      <c r="F391" s="5" t="s">
-        <v>2904</v>
-      </c>
-      <c r="G391" s="5" t="s">
-        <v>2905</v>
-      </c>
-      <c r="H391" s="5" t="s">
-        <v>2906</v>
-      </c>
-      <c r="I391" s="5" t="s">
-        <v>2907</v>
-      </c>
-      <c r="J391" s="5" t="s">
-        <v>2908</v>
-      </c>
-      <c r="K391" s="5" t="s">
-        <v>2909</v>
-      </c>
-      <c r="L391" s="5" t="s">
-        <v>1075</v>
-      </c>
-      <c r="M391" s="5" t="s">
-        <v>2910</v>
-      </c>
-    </row>
-    <row r="392" spans="1:13">
-      <c r="A392" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B392" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C392" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D392" s="5" t="s">
-        <v>2911</v>
-      </c>
-      <c r="E392" s="5" t="s">
-        <v>2912</v>
-      </c>
-      <c r="F392" s="5" t="s">
-        <v>2913</v>
-      </c>
-      <c r="G392" s="5" t="s">
-        <v>2914</v>
-      </c>
-      <c r="H392" s="5" t="s">
-        <v>2915</v>
-      </c>
-      <c r="I392" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J392" s="5" t="s">
-        <v>2916</v>
-      </c>
-      <c r="K392" s="5" t="s">
-        <v>2917</v>
-      </c>
-      <c r="L392" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="M392" s="5" t="s">
-        <v>2918</v>
-      </c>
-    </row>
-    <row r="393" spans="1:13">
-      <c r="A393" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B393" s="5" t="s">
-        <v>2811</v>
-      </c>
-      <c r="C393" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D393" s="5" t="s">
-        <v>2919</v>
-      </c>
-      <c r="E393" s="5" t="s">
-        <v>2920</v>
-      </c>
-      <c r="F393" s="5" t="s">
-        <v>2921</v>
-      </c>
-      <c r="G393" s="5" t="s">
-        <v>2922</v>
-      </c>
-      <c r="H393" s="5" t="s">
-        <v>2923</v>
-      </c>
-      <c r="I393" s="5" t="s">
-        <v>2924</v>
-      </c>
-      <c r="J393" s="5" t="s">
-        <v>2925</v>
-      </c>
-      <c r="K393" s="5" t="s">
-        <v>2926</v>
-      </c>
-      <c r="L393" s="5" t="s">
-        <v>1010</v>
-      </c>
-      <c r="M393" s="5" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="394" spans="1:13">
-      <c r="A394" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B394" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C394" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D394" s="5" t="s">
-        <v>2927</v>
-      </c>
-      <c r="E394" s="5" t="s">
-        <v>2928</v>
-      </c>
-      <c r="F394" s="5" t="s">
-        <v>2929</v>
-      </c>
-      <c r="G394" s="5" t="s">
-        <v>2930</v>
-      </c>
-      <c r="H394" s="5" t="s">
-        <v>2931</v>
-      </c>
-      <c r="I394" s="5" t="s">
-        <v>2932</v>
-      </c>
-      <c r="J394" s="5" t="s">
-        <v>2933</v>
-      </c>
-      <c r="K394" s="5" t="s">
-        <v>2934</v>
-      </c>
-      <c r="L394" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="M394" s="5" t="s">
-        <v>2935</v>
-      </c>
-    </row>
-    <row r="395" spans="1:13">
-      <c r="A395" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B395" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D395" s="5" t="s">
-        <v>2936</v>
-      </c>
-      <c r="E395" s="5" t="s">
-        <v>2937</v>
-      </c>
-      <c r="F395" s="5" t="s">
-        <v>2938</v>
-      </c>
-      <c r="G395" s="5" t="s">
-        <v>2939</v>
-      </c>
-      <c r="H395" s="5" t="s">
-        <v>2940</v>
-      </c>
-      <c r="I395" s="5" t="s">
-        <v>1708</v>
-      </c>
-      <c r="J395" s="5" t="s">
-        <v>2941</v>
-      </c>
-      <c r="K395" s="5" t="s">
-        <v>2942</v>
-      </c>
-      <c r="L395" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="M395" s="5" t="s">
-        <v>2943</v>
-      </c>
-    </row>
-    <row r="396" spans="1:13">
-      <c r="A396" s="5" t="s">
-        <v>2869</v>
-      </c>
-      <c r="B396" s="5" t="s">
-        <v>2667</v>
-      </c>
-      <c r="C396" s="5" t="s">
+    </row>
+    <row r="405" hidden="1" spans="1:14">
+      <c r="A405" s="6" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C405" s="6" t="s">
         <v>2518</v>
       </c>
-      <c r="D396" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E396" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="F396" s="5" t="s">
+      <c r="D405" s="6"/>
+      <c r="E405" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="G396" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="H396" s="5" t="s">
+      <c r="F405" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I396" s="5" t="s">
+      <c r="G405" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="J396" s="5" t="s">
-        <v>1219</v>
-      </c>
-      <c r="K396" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="L396" s="5" t="s">
-        <v>2944</v>
-      </c>
-      <c r="M396" s="5" t="s">
-        <v>441</v>
+      <c r="H405" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I405" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J405" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K405" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L405" s="6"/>
+      <c r="M405" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="406" spans="1:14">
+      <c r="F406" s="1">
+        <f>SUBTOTAL(9,F362:F405)</f>
+        <v>529290</v>
+      </c>
+      <c r="I406" s="1">
+        <f>SUBTOTAL(9,I362:I405)</f>
+        <v>1922</v>
+      </c>
+      <c r="M406" s="1">
+        <f>SUBTOTAL(9,M362:M405)</f>
+        <v>624670</v>
+      </c>
+      <c r="N406">
+        <f>M406/I406*0.085</f>
+        <v>27.6258844953174</v>
+      </c>
+    </row>
+    <row r="407" spans="1:14">
+      <c r="I407" s="1">
+        <f>I406/F406</f>
+        <v>0.00363127963876136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Z361" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:Z361">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Z405" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2026-08-11"/>
+        <filter val="2026-08-12"/>
+        <filter val="2026-08-13"/>
+        <filter val="2026-08-14"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="大神"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A1:Z405">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>

--- a/data/uploads/tongshi_demo.xlsx
+++ b/data/uploads/tongshi_demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11140"/>
+    <workbookView windowWidth="26860" windowHeight="11140"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4576" uniqueCount="2788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4687" uniqueCount="2792">
   <si>
     <t>日期</t>
   </si>
@@ -8394,6 +8394,18 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>20260821</t>
+  </si>
+  <si>
+    <t>20260822</t>
+  </si>
+  <si>
+    <t>20260823</t>
+  </si>
+  <si>
+    <t>20260824</t>
   </si>
 </sst>
 </file>
@@ -9427,7 +9439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z435"/>
+  <dimension ref="A1:Z471"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.0192307692308" style="2" customWidth="1"/>
@@ -27259,6 +27271,1482 @@
         <v>1</v>
       </c>
     </row>
+    <row r="436" s="1" customFormat="1" spans="1:13">
+      <c r="A436" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D436" s="1">
+        <v>0.00313070265021513</v>
+      </c>
+      <c r="E436" s="1">
+        <v>341757</v>
+      </c>
+      <c r="F436" s="1">
+        <v>59731</v>
+      </c>
+      <c r="G436" s="1">
+        <v>12399</v>
+      </c>
+      <c r="H436" s="1">
+        <v>8858</v>
+      </c>
+      <c r="I436" s="1">
+        <v>187</v>
+      </c>
+      <c r="J436" s="1">
+        <v>1491706</v>
+      </c>
+      <c r="K436" s="1">
+        <v>664214</v>
+      </c>
+      <c r="L436" s="1">
+        <v>0.892832755329731</v>
+      </c>
+      <c r="M436" s="1">
+        <v>69087</v>
+      </c>
+    </row>
+    <row r="437" s="1" customFormat="1" spans="1:13">
+      <c r="A437" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C437" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D437" s="1">
+        <v>0.00313070265021513</v>
+      </c>
+      <c r="E437" s="1">
+        <v>341757</v>
+      </c>
+      <c r="F437" s="1">
+        <v>59731</v>
+      </c>
+      <c r="G437" s="1">
+        <v>12399</v>
+      </c>
+      <c r="H437" s="1">
+        <v>8858</v>
+      </c>
+      <c r="I437" s="1">
+        <v>187</v>
+      </c>
+      <c r="J437" s="1">
+        <v>1491706</v>
+      </c>
+      <c r="K437" s="1">
+        <v>664214</v>
+      </c>
+      <c r="L437" s="1">
+        <v>0.892832755329731</v>
+      </c>
+      <c r="M437" s="1">
+        <v>69087</v>
+      </c>
+    </row>
+    <row r="438" s="1" customFormat="1" spans="1:13">
+      <c r="A438" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D438" s="1">
+        <v>0.000714616810877627</v>
+      </c>
+      <c r="E438" s="1">
+        <v>268190</v>
+      </c>
+      <c r="F438" s="1">
+        <v>51776</v>
+      </c>
+      <c r="G438" s="1">
+        <v>4257</v>
+      </c>
+      <c r="H438" s="1">
+        <v>3503</v>
+      </c>
+      <c r="I438" s="1">
+        <v>37</v>
+      </c>
+      <c r="J438" s="1">
+        <v>1083836</v>
+      </c>
+      <c r="K438" s="1">
+        <v>279802</v>
+      </c>
+      <c r="L438" s="1">
+        <v>1.09545846057474</v>
+      </c>
+      <c r="M438" s="1">
+        <v>56653</v>
+      </c>
+    </row>
+    <row r="439" s="1" customFormat="1" spans="1:13">
+      <c r="A439" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C439" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D439" s="1">
+        <v>0.00444972956384978</v>
+      </c>
+      <c r="E439" s="1">
+        <v>206379</v>
+      </c>
+      <c r="F439" s="1">
+        <v>26069</v>
+      </c>
+      <c r="G439" s="1">
+        <v>5741</v>
+      </c>
+      <c r="H439" s="1">
+        <v>4023</v>
+      </c>
+      <c r="I439" s="1">
+        <v>116</v>
+      </c>
+      <c r="J439" s="1">
+        <v>686673</v>
+      </c>
+      <c r="K439" s="1">
+        <v>352068</v>
+      </c>
+      <c r="L439" s="1">
+        <v>1.0220867444696</v>
+      </c>
+      <c r="M439" s="1">
+        <v>31085</v>
+      </c>
+    </row>
+    <row r="440" s="1" customFormat="1" spans="1:13">
+      <c r="A440" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C440" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D440" s="1">
+        <v>0.00434038778355088</v>
+      </c>
+      <c r="E440" s="1">
+        <v>262977</v>
+      </c>
+      <c r="F440" s="1">
+        <v>63128</v>
+      </c>
+      <c r="G440" s="1">
+        <v>19346</v>
+      </c>
+      <c r="H440" s="1">
+        <v>11699</v>
+      </c>
+      <c r="I440" s="1">
+        <v>274</v>
+      </c>
+      <c r="J440" s="1">
+        <v>1321752</v>
+      </c>
+      <c r="K440" s="1">
+        <v>570320</v>
+      </c>
+      <c r="L440" s="1">
+        <v>0.491333264412971</v>
+      </c>
+      <c r="M440" s="1">
+        <v>69789</v>
+      </c>
+    </row>
+    <row r="441" s="1" customFormat="1" spans="1:13">
+      <c r="A441" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C441" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D441" s="1">
+        <v>0.010272759475735</v>
+      </c>
+      <c r="E441" s="1">
+        <v>7647</v>
+      </c>
+      <c r="F441" s="1">
+        <v>2823</v>
+      </c>
+      <c r="G441" s="1">
+        <v>1434</v>
+      </c>
+      <c r="H441" s="1">
+        <v>1203</v>
+      </c>
+      <c r="I441" s="1">
+        <v>29</v>
+      </c>
+      <c r="J441" s="1">
+        <v>71849</v>
+      </c>
+      <c r="K441" s="1">
+        <v>42992</v>
+      </c>
+      <c r="L441" s="1">
+        <v>0.499674569967457</v>
+      </c>
+      <c r="M441" s="1">
+        <v>3256</v>
+      </c>
+    </row>
+    <row r="442" s="1" customFormat="1" spans="1:13">
+      <c r="A442" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D442" s="1">
+        <v>0.0178260869565217</v>
+      </c>
+      <c r="E442" s="1">
+        <v>7193</v>
+      </c>
+      <c r="F442" s="1">
+        <v>2300</v>
+      </c>
+      <c r="G442" s="1">
+        <v>1309</v>
+      </c>
+      <c r="H442" s="1">
+        <v>1094</v>
+      </c>
+      <c r="I442" s="1">
+        <v>41</v>
+      </c>
+      <c r="J442" s="1">
+        <v>74822</v>
+      </c>
+      <c r="K442" s="1">
+        <v>52666</v>
+      </c>
+      <c r="L442" s="1">
+        <v>0.670562770562771</v>
+      </c>
+      <c r="M442" s="1">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="443" s="1" customFormat="1" spans="1:13">
+      <c r="A443" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D443" s="1">
+        <v>0.00777352716143841</v>
+      </c>
+      <c r="E443" s="1">
+        <v>228242</v>
+      </c>
+      <c r="F443" s="1">
+        <v>32675</v>
+      </c>
+      <c r="G443" s="1">
+        <v>10316</v>
+      </c>
+      <c r="H443" s="1">
+        <v>7245</v>
+      </c>
+      <c r="I443" s="1">
+        <v>254</v>
+      </c>
+      <c r="J443" s="1">
+        <v>1158348</v>
+      </c>
+      <c r="K443" s="1">
+        <v>750566</v>
+      </c>
+      <c r="L443" s="1">
+        <v>1.21262440222308</v>
+      </c>
+      <c r="M443" s="1">
+        <v>43463</v>
+      </c>
+    </row>
+    <row r="444" s="1" customFormat="1" spans="1:13">
+      <c r="A444" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C444" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D444" s="1">
+        <v>0.00124432629629106</v>
+      </c>
+      <c r="E444" s="1">
+        <v>261129</v>
+      </c>
+      <c r="F444" s="1">
+        <v>70721</v>
+      </c>
+      <c r="G444" s="1">
+        <v>6991</v>
+      </c>
+      <c r="H444" s="1">
+        <v>5647</v>
+      </c>
+      <c r="I444" s="1">
+        <v>88</v>
+      </c>
+      <c r="J444" s="1">
+        <v>1600046</v>
+      </c>
+      <c r="K444" s="1">
+        <v>490559</v>
+      </c>
+      <c r="L444" s="1">
+        <v>1.1695012635293</v>
+      </c>
+      <c r="M444" s="1">
+        <v>79003</v>
+      </c>
+    </row>
+    <row r="445" s="1" customFormat="1" spans="1:13">
+      <c r="A445" s="1" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D445" s="1">
+        <v>0.00882744237891482</v>
+      </c>
+      <c r="E445" s="1">
+        <v>237659</v>
+      </c>
+      <c r="F445" s="1">
+        <v>55622</v>
+      </c>
+      <c r="G445" s="1">
+        <v>17963</v>
+      </c>
+      <c r="H445" s="1">
+        <v>10958</v>
+      </c>
+      <c r="I445" s="1">
+        <v>491</v>
+      </c>
+      <c r="J445" s="1">
+        <v>1382296</v>
+      </c>
+      <c r="K445" s="1">
+        <v>707907</v>
+      </c>
+      <c r="L445" s="1">
+        <v>0.656819573567889</v>
+      </c>
+      <c r="M445" s="1">
+        <v>64858</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13">
+      <c r="A446" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C446" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D446" s="1">
+        <v>0.00230777552075195</v>
+      </c>
+      <c r="E446" s="1">
+        <v>446369</v>
+      </c>
+      <c r="F446" s="1">
+        <v>83197</v>
+      </c>
+      <c r="G446" s="1">
+        <v>16727</v>
+      </c>
+      <c r="H446" s="1">
+        <v>11492</v>
+      </c>
+      <c r="I446" s="1">
+        <v>192</v>
+      </c>
+      <c r="J446" s="1">
+        <v>1954156</v>
+      </c>
+      <c r="K446" s="1">
+        <v>795743</v>
+      </c>
+      <c r="L446" s="1">
+        <v>0.792872800462326</v>
+      </c>
+      <c r="M446" s="1">
+        <v>94442</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13">
+      <c r="A447" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C447" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D447" s="1">
+        <v>0.00286060072615249</v>
+      </c>
+      <c r="E447" s="1">
+        <v>206536</v>
+      </c>
+      <c r="F447" s="1">
+        <v>27267</v>
+      </c>
+      <c r="G447" s="1">
+        <v>5954</v>
+      </c>
+      <c r="H447" s="1">
+        <v>4079</v>
+      </c>
+      <c r="I447" s="1">
+        <v>78</v>
+      </c>
+      <c r="J447" s="1">
+        <v>661690</v>
+      </c>
+      <c r="K447" s="1">
+        <v>306033</v>
+      </c>
+      <c r="L447" s="1">
+        <v>0.856659388646288</v>
+      </c>
+      <c r="M447" s="1">
+        <v>31537</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13">
+      <c r="A448" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C448" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D448" s="1">
+        <v>0.000635011350827896</v>
+      </c>
+      <c r="E448" s="1">
+        <v>354254</v>
+      </c>
+      <c r="F448" s="1">
+        <v>62991</v>
+      </c>
+      <c r="G448" s="1">
+        <v>5488</v>
+      </c>
+      <c r="H448" s="1">
+        <v>4497</v>
+      </c>
+      <c r="I448" s="1">
+        <v>40</v>
+      </c>
+      <c r="J448" s="1">
+        <v>1358353</v>
+      </c>
+      <c r="K448" s="1">
+        <v>349445</v>
+      </c>
+      <c r="L448" s="1">
+        <v>1.0612396744412</v>
+      </c>
+      <c r="M448" s="1">
+        <v>69146</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13">
+      <c r="A449" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C449" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D449" s="1">
+        <v>0.00449846446645616</v>
+      </c>
+      <c r="E449" s="1">
+        <v>174319</v>
+      </c>
+      <c r="F449" s="1">
+        <v>46238</v>
+      </c>
+      <c r="G449" s="1">
+        <v>18076</v>
+      </c>
+      <c r="H449" s="1">
+        <v>10119</v>
+      </c>
+      <c r="I449" s="1">
+        <v>208</v>
+      </c>
+      <c r="J449" s="1">
+        <v>989774</v>
+      </c>
+      <c r="K449" s="1">
+        <v>469460</v>
+      </c>
+      <c r="L449" s="1">
+        <v>0.432857564357896</v>
+      </c>
+      <c r="M449" s="1">
+        <v>51580</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13">
+      <c r="A450" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D450" s="1">
+        <v>0.00966486757876239</v>
+      </c>
+      <c r="E450" s="1">
+        <v>20042</v>
+      </c>
+      <c r="F450" s="1">
+        <v>7967</v>
+      </c>
+      <c r="G450" s="1">
+        <v>4063</v>
+      </c>
+      <c r="H450" s="1">
+        <v>3457</v>
+      </c>
+      <c r="I450" s="1">
+        <v>77</v>
+      </c>
+      <c r="J450" s="1">
+        <v>214244</v>
+      </c>
+      <c r="K450" s="1">
+        <v>134993</v>
+      </c>
+      <c r="L450" s="1">
+        <v>0.553749282139634</v>
+      </c>
+      <c r="M450" s="1">
+        <v>9435</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13">
+      <c r="A451" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C451" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D451" s="1">
+        <v>0.000927500386458494</v>
+      </c>
+      <c r="E451" s="1">
+        <v>206867</v>
+      </c>
+      <c r="F451" s="1">
+        <v>51752</v>
+      </c>
+      <c r="G451" s="1">
+        <v>6034</v>
+      </c>
+      <c r="H451" s="1">
+        <v>4766</v>
+      </c>
+      <c r="I451" s="1">
+        <v>48</v>
+      </c>
+      <c r="J451" s="1">
+        <v>1145521</v>
+      </c>
+      <c r="K451" s="1">
+        <v>328299</v>
+      </c>
+      <c r="L451" s="1">
+        <v>0.906803115677826</v>
+      </c>
+      <c r="M451" s="1">
+        <v>57137</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13">
+      <c r="A452" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D452" s="1">
+        <v>0.00419054777788218</v>
+      </c>
+      <c r="E452" s="1">
+        <v>397059</v>
+      </c>
+      <c r="F452" s="1">
+        <v>53215</v>
+      </c>
+      <c r="G452" s="1">
+        <v>10646</v>
+      </c>
+      <c r="H452" s="1">
+        <v>7701</v>
+      </c>
+      <c r="I452" s="1">
+        <v>223</v>
+      </c>
+      <c r="J452" s="1">
+        <v>1443735</v>
+      </c>
+      <c r="K452" s="1">
+        <v>700444</v>
+      </c>
+      <c r="L452" s="1">
+        <v>1.09656835118041</v>
+      </c>
+      <c r="M452" s="1">
+        <v>63732</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13">
+      <c r="A453" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D453" s="1">
+        <v>0.00831980179788071</v>
+      </c>
+      <c r="E453" s="1">
+        <v>277788</v>
+      </c>
+      <c r="F453" s="1">
+        <v>59737</v>
+      </c>
+      <c r="G453" s="1">
+        <v>18292</v>
+      </c>
+      <c r="H453" s="1">
+        <v>11012</v>
+      </c>
+      <c r="I453" s="1">
+        <v>497</v>
+      </c>
+      <c r="J453" s="1">
+        <v>1418397</v>
+      </c>
+      <c r="K453" s="1">
+        <v>689174</v>
+      </c>
+      <c r="L453" s="1">
+        <v>0.62793753189008</v>
+      </c>
+      <c r="M453" s="1">
+        <v>68771</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13">
+      <c r="A454" s="1" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C454" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D454" s="1">
+        <v>0.0185471406491499</v>
+      </c>
+      <c r="E454" s="1">
+        <v>2307</v>
+      </c>
+      <c r="F454" s="1">
+        <v>647</v>
+      </c>
+      <c r="G454" s="1">
+        <v>402</v>
+      </c>
+      <c r="H454" s="1">
+        <v>343</v>
+      </c>
+      <c r="I454" s="1">
+        <v>12</v>
+      </c>
+      <c r="J454" s="1">
+        <v>22330</v>
+      </c>
+      <c r="K454" s="1">
+        <v>17057</v>
+      </c>
+      <c r="L454" s="1">
+        <v>0.707172470978441</v>
+      </c>
+      <c r="M454" s="1">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13">
+      <c r="A455" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C455" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D455" s="1">
+        <v>0.00133877769596359</v>
+      </c>
+      <c r="E455" s="1">
+        <v>516796</v>
+      </c>
+      <c r="F455" s="1">
+        <v>89634</v>
+      </c>
+      <c r="G455" s="1">
+        <v>16150</v>
+      </c>
+      <c r="H455" s="1">
+        <v>11166</v>
+      </c>
+      <c r="I455" s="1">
+        <v>120</v>
+      </c>
+      <c r="J455" s="1">
+        <v>1935602</v>
+      </c>
+      <c r="K455" s="1">
+        <v>662681</v>
+      </c>
+      <c r="L455" s="1">
+        <v>0.683881320949432</v>
+      </c>
+      <c r="M455" s="1">
+        <v>98915</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13">
+      <c r="A456" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D456" s="1">
+        <v>0.00311826919985855</v>
+      </c>
+      <c r="E456" s="1">
+        <v>251608</v>
+      </c>
+      <c r="F456" s="1">
+        <v>62214</v>
+      </c>
+      <c r="G456" s="1">
+        <v>12520</v>
+      </c>
+      <c r="H456" s="1">
+        <v>8045</v>
+      </c>
+      <c r="I456" s="1">
+        <v>194</v>
+      </c>
+      <c r="J456" s="1">
+        <v>1267322</v>
+      </c>
+      <c r="K456" s="1">
+        <v>432037</v>
+      </c>
+      <c r="L456" s="1">
+        <v>0.575129126730564</v>
+      </c>
+      <c r="M456" s="1">
+        <v>68019</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13">
+      <c r="A457" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C457" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D457" s="1">
+        <v>0.000622719110235764</v>
+      </c>
+      <c r="E457" s="1">
+        <v>390014</v>
+      </c>
+      <c r="F457" s="1">
+        <v>69052</v>
+      </c>
+      <c r="G457" s="1">
+        <v>4582</v>
+      </c>
+      <c r="H457" s="1">
+        <v>3836</v>
+      </c>
+      <c r="I457" s="1">
+        <v>43</v>
+      </c>
+      <c r="J457" s="1">
+        <v>1399666</v>
+      </c>
+      <c r="K457" s="1">
+        <v>298512</v>
+      </c>
+      <c r="L457" s="1">
+        <v>1.08581405499782</v>
+      </c>
+      <c r="M457" s="1">
+        <v>74756</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13">
+      <c r="A458" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D458" s="1">
+        <v>0.0097058384351202</v>
+      </c>
+      <c r="E458" s="1">
+        <v>19765</v>
+      </c>
+      <c r="F458" s="1">
+        <v>6697</v>
+      </c>
+      <c r="G458" s="1">
+        <v>3265</v>
+      </c>
+      <c r="H458" s="1">
+        <v>2796</v>
+      </c>
+      <c r="I458" s="1">
+        <v>65</v>
+      </c>
+      <c r="J458" s="1">
+        <v>177062</v>
+      </c>
+      <c r="K458" s="1">
+        <v>110380</v>
+      </c>
+      <c r="L458" s="1">
+        <v>0.563450740173558</v>
+      </c>
+      <c r="M458" s="1">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13">
+      <c r="A459" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C459" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D459" s="1">
+        <v>0.00286630392537894</v>
+      </c>
+      <c r="E459" s="1">
+        <v>210179</v>
+      </c>
+      <c r="F459" s="1">
+        <v>20584</v>
+      </c>
+      <c r="G459" s="1">
+        <v>4220</v>
+      </c>
+      <c r="H459" s="1">
+        <v>2918</v>
+      </c>
+      <c r="I459" s="1">
+        <v>59</v>
+      </c>
+      <c r="J459" s="1">
+        <v>497278</v>
+      </c>
+      <c r="K459" s="1">
+        <v>220111</v>
+      </c>
+      <c r="L459" s="1">
+        <v>0.869316745655608</v>
+      </c>
+      <c r="M459" s="1">
+        <v>23725</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13">
+      <c r="A460" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D460" s="1">
+        <v>0.000423539901917075</v>
+      </c>
+      <c r="E460" s="1">
+        <v>306936</v>
+      </c>
+      <c r="F460" s="1">
+        <v>89720</v>
+      </c>
+      <c r="G460" s="1">
+        <v>6628</v>
+      </c>
+      <c r="H460" s="1">
+        <v>5378</v>
+      </c>
+      <c r="I460" s="1">
+        <v>38</v>
+      </c>
+      <c r="J460" s="1">
+        <v>1823506</v>
+      </c>
+      <c r="K460" s="1">
+        <v>369903</v>
+      </c>
+      <c r="L460" s="1">
+        <v>0.930152383826192</v>
+      </c>
+      <c r="M460" s="1">
+        <v>96636</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13">
+      <c r="A461" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C461" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D461" s="1">
+        <v>0.0234375</v>
+      </c>
+      <c r="E461" s="1">
+        <v>1017</v>
+      </c>
+      <c r="F461" s="1">
+        <v>128</v>
+      </c>
+      <c r="G461" s="1">
+        <v>77</v>
+      </c>
+      <c r="H461" s="1">
+        <v>66</v>
+      </c>
+      <c r="I461" s="1">
+        <v>3</v>
+      </c>
+      <c r="J461" s="1">
+        <v>4088</v>
+      </c>
+      <c r="K461" s="1">
+        <v>2901</v>
+      </c>
+      <c r="L461" s="1">
+        <v>0.627922077922078</v>
+      </c>
+      <c r="M461" s="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="462" spans="1:13">
+      <c r="A462" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C462" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D462" s="1">
+        <v>0.00264300306435138</v>
+      </c>
+      <c r="E462" s="1">
+        <v>615040</v>
+      </c>
+      <c r="F462" s="1">
+        <v>78320</v>
+      </c>
+      <c r="G462" s="1">
+        <v>12387</v>
+      </c>
+      <c r="H462" s="1">
+        <v>9340</v>
+      </c>
+      <c r="I462" s="1">
+        <v>207</v>
+      </c>
+      <c r="J462" s="1">
+        <v>1930335</v>
+      </c>
+      <c r="K462" s="1">
+        <v>799513</v>
+      </c>
+      <c r="L462" s="1">
+        <v>1.07574204138748</v>
+      </c>
+      <c r="M462" s="1">
+        <v>90662</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13">
+      <c r="A463" s="1" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C463" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D463" s="1">
+        <v>0.0035233483861363</v>
+      </c>
+      <c r="E463" s="1">
+        <v>511868</v>
+      </c>
+      <c r="F463" s="1">
+        <v>141059</v>
+      </c>
+      <c r="G463" s="1">
+        <v>21950</v>
+      </c>
+      <c r="H463" s="1">
+        <v>14749</v>
+      </c>
+      <c r="I463" s="1">
+        <v>497</v>
+      </c>
+      <c r="J463" s="1">
+        <v>2816202</v>
+      </c>
+      <c r="K463" s="1">
+        <v>903087</v>
+      </c>
+      <c r="L463" s="1">
+        <v>0.685715261958998</v>
+      </c>
+      <c r="M463" s="1">
+        <v>154108</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13">
+      <c r="A464" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D464" s="1">
+        <v>0</v>
+      </c>
+      <c r="E464" s="1">
+        <v>19</v>
+      </c>
+      <c r="F464" s="1">
+        <v>5</v>
+      </c>
+      <c r="G464" s="1">
+        <v>0</v>
+      </c>
+      <c r="H464" s="1">
+        <v>0</v>
+      </c>
+      <c r="I464" s="1">
+        <v>0</v>
+      </c>
+      <c r="J464" s="1">
+        <v>64</v>
+      </c>
+      <c r="K464" s="1">
+        <v>0</v>
+      </c>
+      <c r="L464" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="M464" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13">
+      <c r="A465" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C465" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E465" s="1">
+        <v>1</v>
+      </c>
+      <c r="F465" s="1">
+        <v>0</v>
+      </c>
+      <c r="G465" s="1">
+        <v>0</v>
+      </c>
+      <c r="H465" s="1">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>0</v>
+      </c>
+      <c r="J465" s="1">
+        <v>0</v>
+      </c>
+      <c r="K465" s="1">
+        <v>0</v>
+      </c>
+      <c r="L465" s="1" t="s">
+        <v>2787</v>
+      </c>
+      <c r="M465" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13">
+      <c r="A466" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C466" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D466" s="1">
+        <v>0</v>
+      </c>
+      <c r="E466" s="1">
+        <v>19</v>
+      </c>
+      <c r="F466" s="1">
+        <v>3</v>
+      </c>
+      <c r="G466" s="1">
+        <v>1</v>
+      </c>
+      <c r="H466" s="1">
+        <v>1</v>
+      </c>
+      <c r="I466" s="1">
+        <v>0</v>
+      </c>
+      <c r="J466" s="1">
+        <v>72</v>
+      </c>
+      <c r="K466" s="1">
+        <v>12</v>
+      </c>
+      <c r="L466" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="M466" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13">
+      <c r="A467" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C467" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D467" s="1">
+        <v>0.00410576449334866</v>
+      </c>
+      <c r="E467" s="1">
+        <v>51444</v>
+      </c>
+      <c r="F467" s="1">
+        <v>18267</v>
+      </c>
+      <c r="G467" s="1">
+        <v>3584</v>
+      </c>
+      <c r="H467" s="1">
+        <v>2170</v>
+      </c>
+      <c r="I467" s="1">
+        <v>75</v>
+      </c>
+      <c r="J467" s="1">
+        <v>372861</v>
+      </c>
+      <c r="K467" s="1">
+        <v>117798</v>
+      </c>
+      <c r="L467" s="1">
+        <v>0.547795758928571</v>
+      </c>
+      <c r="M467" s="1">
+        <v>19920</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13">
+      <c r="A468" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D468" s="1">
+        <v>0.000926406284740236</v>
+      </c>
+      <c r="E468" s="1">
+        <v>236872</v>
+      </c>
+      <c r="F468" s="1">
+        <v>53972</v>
+      </c>
+      <c r="G468" s="1">
+        <v>4319</v>
+      </c>
+      <c r="H468" s="1">
+        <v>3483</v>
+      </c>
+      <c r="I468" s="1">
+        <v>50</v>
+      </c>
+      <c r="J468" s="1">
+        <v>1075151</v>
+      </c>
+      <c r="K468" s="1">
+        <v>275551</v>
+      </c>
+      <c r="L468" s="1">
+        <v>1.06332870263178</v>
+      </c>
+      <c r="M468" s="1">
+        <v>58612</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13">
+      <c r="A469" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>2658</v>
+      </c>
+      <c r="C469" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D469" s="1">
+        <v>0.0104905223556649</v>
+      </c>
+      <c r="E469" s="1">
+        <v>71095</v>
+      </c>
+      <c r="F469" s="1">
+        <v>13822</v>
+      </c>
+      <c r="G469" s="1">
+        <v>3367</v>
+      </c>
+      <c r="H469" s="1">
+        <v>2105</v>
+      </c>
+      <c r="I469" s="1">
+        <v>145</v>
+      </c>
+      <c r="J469" s="1">
+        <v>337725</v>
+      </c>
+      <c r="K469" s="1">
+        <v>153451</v>
+      </c>
+      <c r="L469" s="1">
+        <v>0.75958320958321</v>
+      </c>
+      <c r="M469" s="1">
+        <v>16029</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13">
+      <c r="A470" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D470" s="1">
+        <v>0.00124494242141301</v>
+      </c>
+      <c r="E470" s="1">
+        <v>122252</v>
+      </c>
+      <c r="F470" s="1">
+        <v>25704</v>
+      </c>
+      <c r="G470" s="1">
+        <v>3073</v>
+      </c>
+      <c r="H470" s="1">
+        <v>2376</v>
+      </c>
+      <c r="I470" s="1">
+        <v>32</v>
+      </c>
+      <c r="J470" s="1">
+        <v>581149</v>
+      </c>
+      <c r="K470" s="1">
+        <v>198591</v>
+      </c>
+      <c r="L470" s="1">
+        <v>1.07707452001302</v>
+      </c>
+      <c r="M470" s="1">
+        <v>28829</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13">
+      <c r="A471" s="1" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D471" s="1">
+        <v>0</v>
+      </c>
+      <c r="E471" s="1">
+        <v>44</v>
+      </c>
+      <c r="F471" s="1">
+        <v>15</v>
+      </c>
+      <c r="G471" s="1">
+        <v>3</v>
+      </c>
+      <c r="H471" s="1">
+        <v>3</v>
+      </c>
+      <c r="I471" s="1">
+        <v>0</v>
+      </c>
+      <c r="J471" s="1">
+        <v>266</v>
+      </c>
+      <c r="K471" s="1">
+        <v>27</v>
+      </c>
+      <c r="L471" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="M471" s="1">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Z418" etc:filterBottomFollowUsedRange="0">
     <extLst/>
